--- a/data/proc_data/private_data/2025_c_educativo.xlsx
+++ b/data/proc_data/private_data/2025_c_educativo.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH346"/>
+  <dimension ref="A1:AJ346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -525,6 +525,16 @@
           <t>c_tramo_2025</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>c_ranking_2024</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>c_ranking_2025</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -637,6 +647,12 @@
       <c r="AH2">
         <v>3</v>
       </c>
+      <c r="AI2">
+        <v>178</v>
+      </c>
+      <c r="AJ2">
+        <v>123</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +765,12 @@
       <c r="AH3">
         <v>1</v>
       </c>
+      <c r="AI3">
+        <v>283</v>
+      </c>
+      <c r="AJ3">
+        <v>278</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -919,6 +941,12 @@
       <c r="AH5">
         <v>2</v>
       </c>
+      <c r="AI5">
+        <v>208</v>
+      </c>
+      <c r="AJ5">
+        <v>215</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1031,6 +1059,12 @@
       <c r="AH6">
         <v>1</v>
       </c>
+      <c r="AI6">
+        <v>296</v>
+      </c>
+      <c r="AJ6">
+        <v>257</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1143,6 +1177,12 @@
       <c r="AH7">
         <v>3</v>
       </c>
+      <c r="AI7">
+        <v>42</v>
+      </c>
+      <c r="AJ7">
+        <v>82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1255,6 +1295,12 @@
       <c r="AH8">
         <v>3</v>
       </c>
+      <c r="AI8">
+        <v>258</v>
+      </c>
+      <c r="AJ8">
+        <v>112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1367,6 +1413,12 @@
       <c r="AH9">
         <v>1</v>
       </c>
+      <c r="AI9">
+        <v>274</v>
+      </c>
+      <c r="AJ9">
+        <v>288</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1479,6 +1531,12 @@
       <c r="AH10">
         <v>2</v>
       </c>
+      <c r="AI10">
+        <v>187</v>
+      </c>
+      <c r="AJ10">
+        <v>163</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1591,6 +1649,12 @@
       <c r="AH11">
         <v>1</v>
       </c>
+      <c r="AI11">
+        <v>272</v>
+      </c>
+      <c r="AJ11">
+        <v>244</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1703,6 +1767,12 @@
       <c r="AH12">
         <v>1</v>
       </c>
+      <c r="AI12">
+        <v>141</v>
+      </c>
+      <c r="AJ12">
+        <v>237</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1815,6 +1885,12 @@
       <c r="AH13">
         <v>1</v>
       </c>
+      <c r="AI13">
+        <v>112</v>
+      </c>
+      <c r="AJ13">
+        <v>229</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1927,6 +2003,12 @@
       <c r="AH14">
         <v>1</v>
       </c>
+      <c r="AI14">
+        <v>269</v>
+      </c>
+      <c r="AJ14">
+        <v>271</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2009,6 +2091,9 @@
       <c r="X15">
         <v>3</v>
       </c>
+      <c r="AI15">
+        <v>115</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2131,6 +2216,9 @@
       <c r="X17">
         <v>3.5</v>
       </c>
+      <c r="AI17">
+        <v>224</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2243,6 +2331,12 @@
       <c r="AH18">
         <v>2</v>
       </c>
+      <c r="AI18">
+        <v>192</v>
+      </c>
+      <c r="AJ18">
+        <v>198</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2346,6 +2440,9 @@
       <c r="AF19">
         <v>2</v>
       </c>
+      <c r="AI19">
+        <v>295</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2458,6 +2555,12 @@
       <c r="AH20">
         <v>4</v>
       </c>
+      <c r="AI20">
+        <v>103</v>
+      </c>
+      <c r="AJ20">
+        <v>40</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2570,6 +2673,12 @@
       <c r="AH21">
         <v>2</v>
       </c>
+      <c r="AI21">
+        <v>127</v>
+      </c>
+      <c r="AJ21">
+        <v>161</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2652,6 +2761,9 @@
       <c r="X22">
         <v>3</v>
       </c>
+      <c r="AI22">
+        <v>263</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2764,6 +2876,12 @@
       <c r="AH23">
         <v>2</v>
       </c>
+      <c r="AI23">
+        <v>63</v>
+      </c>
+      <c r="AJ23">
+        <v>155</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2876,6 +2994,12 @@
       <c r="AH24">
         <v>3</v>
       </c>
+      <c r="AI24">
+        <v>24</v>
+      </c>
+      <c r="AJ24">
+        <v>75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2988,6 +3112,12 @@
       <c r="AH25">
         <v>3</v>
       </c>
+      <c r="AI25">
+        <v>80</v>
+      </c>
+      <c r="AJ25">
+        <v>91</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3128,6 +3258,9 @@
       <c r="X27">
         <v>3</v>
       </c>
+      <c r="AI27">
+        <v>299</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3210,6 +3343,9 @@
       <c r="X28">
         <v>3.5</v>
       </c>
+      <c r="AI28">
+        <v>287</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3298,6 +3434,9 @@
       <c r="AH29">
         <v>1</v>
       </c>
+      <c r="AJ29">
+        <v>257</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3401,6 +3540,9 @@
       <c r="AF30">
         <v>2</v>
       </c>
+      <c r="AI30">
+        <v>31</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3571,6 +3713,12 @@
       <c r="AH32">
         <v>2</v>
       </c>
+      <c r="AI32">
+        <v>208</v>
+      </c>
+      <c r="AJ32">
+        <v>216</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3683,6 +3831,12 @@
       <c r="AH33">
         <v>4</v>
       </c>
+      <c r="AI33">
+        <v>16</v>
+      </c>
+      <c r="AJ33">
+        <v>23</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3795,6 +3949,12 @@
       <c r="AH34">
         <v>3</v>
       </c>
+      <c r="AI34">
+        <v>178</v>
+      </c>
+      <c r="AJ34">
+        <v>104</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3929,6 +4089,12 @@
       <c r="AH36">
         <v>3</v>
       </c>
+      <c r="AI36">
+        <v>100</v>
+      </c>
+      <c r="AJ36">
+        <v>106</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4041,6 +4207,12 @@
       <c r="AH37">
         <v>4</v>
       </c>
+      <c r="AI37">
+        <v>105</v>
+      </c>
+      <c r="AJ37">
+        <v>13</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4211,6 +4383,12 @@
       <c r="AH39">
         <v>3</v>
       </c>
+      <c r="AI39">
+        <v>245</v>
+      </c>
+      <c r="AJ39">
+        <v>99</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4421,6 +4599,12 @@
       <c r="AH42">
         <v>4</v>
       </c>
+      <c r="AI42">
+        <v>56</v>
+      </c>
+      <c r="AJ42">
+        <v>67</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4591,6 +4775,12 @@
       <c r="AH44">
         <v>2</v>
       </c>
+      <c r="AI44">
+        <v>122</v>
+      </c>
+      <c r="AJ44">
+        <v>197</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4845,6 +5035,12 @@
       <c r="AH49">
         <v>4</v>
       </c>
+      <c r="AI49">
+        <v>111</v>
+      </c>
+      <c r="AJ49">
+        <v>32</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5019,6 +5215,12 @@
       <c r="AH52">
         <v>1</v>
       </c>
+      <c r="AI52">
+        <v>265</v>
+      </c>
+      <c r="AJ52">
+        <v>226</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5153,6 +5355,12 @@
       <c r="AH54">
         <v>2</v>
       </c>
+      <c r="AI54">
+        <v>252</v>
+      </c>
+      <c r="AJ54">
+        <v>202</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5265,6 +5473,12 @@
       <c r="AH55">
         <v>3</v>
       </c>
+      <c r="AI55">
+        <v>217</v>
+      </c>
+      <c r="AJ55">
+        <v>133</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5377,6 +5591,12 @@
       <c r="AH56">
         <v>4</v>
       </c>
+      <c r="AI56">
+        <v>137</v>
+      </c>
+      <c r="AJ56">
+        <v>61</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5489,6 +5709,12 @@
       <c r="AH57">
         <v>3</v>
       </c>
+      <c r="AI57">
+        <v>229</v>
+      </c>
+      <c r="AJ57">
+        <v>122</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5601,6 +5827,12 @@
       <c r="AH58">
         <v>2</v>
       </c>
+      <c r="AI58">
+        <v>182</v>
+      </c>
+      <c r="AJ58">
+        <v>168</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5713,6 +5945,12 @@
       <c r="AH59">
         <v>2</v>
       </c>
+      <c r="AI59">
+        <v>187</v>
+      </c>
+      <c r="AJ59">
+        <v>212</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5825,6 +6063,12 @@
       <c r="AH60">
         <v>4</v>
       </c>
+      <c r="AI60">
+        <v>52</v>
+      </c>
+      <c r="AJ60">
+        <v>36</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5937,6 +6181,12 @@
       <c r="AH61">
         <v>4</v>
       </c>
+      <c r="AI61">
+        <v>108</v>
+      </c>
+      <c r="AJ61">
+        <v>46</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6049,6 +6299,12 @@
       <c r="AH62">
         <v>3</v>
       </c>
+      <c r="AI62">
+        <v>232</v>
+      </c>
+      <c r="AJ62">
+        <v>74</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6161,6 +6417,12 @@
       <c r="AH63">
         <v>3</v>
       </c>
+      <c r="AI63">
+        <v>256</v>
+      </c>
+      <c r="AJ63">
+        <v>117</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6273,6 +6535,12 @@
       <c r="AH64">
         <v>4</v>
       </c>
+      <c r="AI64">
+        <v>41</v>
+      </c>
+      <c r="AJ64">
+        <v>31</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6385,6 +6653,12 @@
       <c r="AH65">
         <v>3</v>
       </c>
+      <c r="AI65">
+        <v>93</v>
+      </c>
+      <c r="AJ65">
+        <v>78</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6497,6 +6771,12 @@
       <c r="AH66">
         <v>3</v>
       </c>
+      <c r="AI66">
+        <v>243</v>
+      </c>
+      <c r="AJ66">
+        <v>127</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6609,6 +6889,12 @@
       <c r="AH67">
         <v>4</v>
       </c>
+      <c r="AI67">
+        <v>60</v>
+      </c>
+      <c r="AJ67">
+        <v>62</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6721,6 +7007,12 @@
       <c r="AH68">
         <v>3</v>
       </c>
+      <c r="AI68">
+        <v>50</v>
+      </c>
+      <c r="AJ68">
+        <v>73</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6833,6 +7125,12 @@
       <c r="AH69">
         <v>2</v>
       </c>
+      <c r="AI69">
+        <v>95</v>
+      </c>
+      <c r="AJ69">
+        <v>192</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6945,6 +7243,12 @@
       <c r="AH70">
         <v>2</v>
       </c>
+      <c r="AI70">
+        <v>276</v>
+      </c>
+      <c r="AJ70">
+        <v>167</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7057,6 +7361,12 @@
       <c r="AH71">
         <v>2</v>
       </c>
+      <c r="AI71">
+        <v>194</v>
+      </c>
+      <c r="AJ71">
+        <v>185</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7169,6 +7479,12 @@
       <c r="AH72">
         <v>2</v>
       </c>
+      <c r="AI72">
+        <v>261</v>
+      </c>
+      <c r="AJ72">
+        <v>174</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7281,6 +7597,12 @@
       <c r="AH73">
         <v>2</v>
       </c>
+      <c r="AI73">
+        <v>253</v>
+      </c>
+      <c r="AJ73">
+        <v>169</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7393,6 +7715,12 @@
       <c r="AH74">
         <v>4</v>
       </c>
+      <c r="AI74">
+        <v>46</v>
+      </c>
+      <c r="AJ74">
+        <v>16</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7505,6 +7833,12 @@
       <c r="AH75">
         <v>2</v>
       </c>
+      <c r="AI75">
+        <v>250</v>
+      </c>
+      <c r="AJ75">
+        <v>180</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7617,6 +7951,12 @@
       <c r="AH76">
         <v>3</v>
       </c>
+      <c r="AI76">
+        <v>159</v>
+      </c>
+      <c r="AJ76">
+        <v>125</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7729,6 +8069,12 @@
       <c r="AH77">
         <v>3</v>
       </c>
+      <c r="AI77">
+        <v>237</v>
+      </c>
+      <c r="AJ77">
+        <v>98</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7841,6 +8187,12 @@
       <c r="AH78">
         <v>3</v>
       </c>
+      <c r="AI78">
+        <v>241</v>
+      </c>
+      <c r="AJ78">
+        <v>111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7953,6 +8305,12 @@
       <c r="AH79">
         <v>2</v>
       </c>
+      <c r="AI79">
+        <v>174</v>
+      </c>
+      <c r="AJ79">
+        <v>150</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8065,6 +8423,12 @@
       <c r="AH80">
         <v>4</v>
       </c>
+      <c r="AI80">
+        <v>90</v>
+      </c>
+      <c r="AJ80">
+        <v>53</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8177,6 +8541,12 @@
       <c r="AH81">
         <v>1</v>
       </c>
+      <c r="AI81">
+        <v>122</v>
+      </c>
+      <c r="AJ81">
+        <v>218</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8289,6 +8659,12 @@
       <c r="AH82">
         <v>1</v>
       </c>
+      <c r="AI82">
+        <v>250</v>
+      </c>
+      <c r="AJ82">
+        <v>242</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8401,6 +8777,12 @@
       <c r="AH83">
         <v>3</v>
       </c>
+      <c r="AI83">
+        <v>203</v>
+      </c>
+      <c r="AJ83">
+        <v>130</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8513,6 +8895,12 @@
       <c r="AH84">
         <v>4</v>
       </c>
+      <c r="AI84">
+        <v>16</v>
+      </c>
+      <c r="AJ84">
+        <v>6</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8625,6 +9013,12 @@
       <c r="AH85">
         <v>3</v>
       </c>
+      <c r="AI85">
+        <v>93</v>
+      </c>
+      <c r="AJ85">
+        <v>83</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8737,6 +9131,12 @@
       <c r="AH86">
         <v>2</v>
       </c>
+      <c r="AI86">
+        <v>206</v>
+      </c>
+      <c r="AJ86">
+        <v>146</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8849,6 +9249,12 @@
       <c r="AH87">
         <v>4</v>
       </c>
+      <c r="AI87">
+        <v>271</v>
+      </c>
+      <c r="AJ87">
+        <v>38</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8961,6 +9367,12 @@
       <c r="AH88">
         <v>2</v>
       </c>
+      <c r="AI88">
+        <v>284</v>
+      </c>
+      <c r="AJ88">
+        <v>164</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9073,6 +9485,12 @@
       <c r="AH89">
         <v>4</v>
       </c>
+      <c r="AI89">
+        <v>157</v>
+      </c>
+      <c r="AJ89">
+        <v>69</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9185,6 +9603,12 @@
       <c r="AH90">
         <v>3</v>
       </c>
+      <c r="AI90">
+        <v>260</v>
+      </c>
+      <c r="AJ90">
+        <v>124</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9297,6 +9721,12 @@
       <c r="AH91">
         <v>1</v>
       </c>
+      <c r="AI91">
+        <v>300</v>
+      </c>
+      <c r="AJ91">
+        <v>282</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9409,6 +9839,12 @@
       <c r="AH92">
         <v>3</v>
       </c>
+      <c r="AI92">
+        <v>220</v>
+      </c>
+      <c r="AJ92">
+        <v>108</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9521,6 +9957,12 @@
       <c r="AH93">
         <v>2</v>
       </c>
+      <c r="AI93">
+        <v>244</v>
+      </c>
+      <c r="AJ93">
+        <v>177</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9633,6 +10075,12 @@
       <c r="AH94">
         <v>2</v>
       </c>
+      <c r="AI94">
+        <v>86</v>
+      </c>
+      <c r="AJ94">
+        <v>170</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9745,6 +10193,12 @@
       <c r="AH95">
         <v>4</v>
       </c>
+      <c r="AI95">
+        <v>196</v>
+      </c>
+      <c r="AJ95">
+        <v>52</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9857,6 +10311,12 @@
       <c r="AH96">
         <v>3</v>
       </c>
+      <c r="AI96">
+        <v>172</v>
+      </c>
+      <c r="AJ96">
+        <v>87</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9969,6 +10429,12 @@
       <c r="AH97">
         <v>1</v>
       </c>
+      <c r="AI97">
+        <v>253</v>
+      </c>
+      <c r="AJ97">
+        <v>266</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10081,6 +10547,12 @@
       <c r="AH98">
         <v>4</v>
       </c>
+      <c r="AI98">
+        <v>139</v>
+      </c>
+      <c r="AJ98">
+        <v>35</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10163,6 +10635,9 @@
       <c r="X99">
         <v>2.444444444444445</v>
       </c>
+      <c r="AI99">
+        <v>278</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10266,6 +10741,9 @@
       <c r="AF100">
         <v>2</v>
       </c>
+      <c r="AI100">
+        <v>241</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10378,6 +10856,12 @@
       <c r="AH101">
         <v>4</v>
       </c>
+      <c r="AI101">
+        <v>163</v>
+      </c>
+      <c r="AJ101">
+        <v>47</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10490,6 +10974,12 @@
       <c r="AH102">
         <v>2</v>
       </c>
+      <c r="AI102">
+        <v>257</v>
+      </c>
+      <c r="AJ102">
+        <v>166</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10602,6 +11092,12 @@
       <c r="AH103">
         <v>1</v>
       </c>
+      <c r="AI103">
+        <v>290</v>
+      </c>
+      <c r="AJ103">
+        <v>270</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10714,6 +11210,12 @@
       <c r="AH104">
         <v>4</v>
       </c>
+      <c r="AI104">
+        <v>113</v>
+      </c>
+      <c r="AJ104">
+        <v>17</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10826,6 +11328,12 @@
       <c r="AH105">
         <v>4</v>
       </c>
+      <c r="AI105">
+        <v>175</v>
+      </c>
+      <c r="AJ105">
+        <v>43</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10938,6 +11446,12 @@
       <c r="AH106">
         <v>2</v>
       </c>
+      <c r="AI106">
+        <v>169</v>
+      </c>
+      <c r="AJ106">
+        <v>165</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11224,6 +11738,12 @@
       <c r="AH110">
         <v>1</v>
       </c>
+      <c r="AI110">
+        <v>98</v>
+      </c>
+      <c r="AJ110">
+        <v>263</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11336,6 +11856,12 @@
       <c r="AH111">
         <v>2</v>
       </c>
+      <c r="AI111">
+        <v>224</v>
+      </c>
+      <c r="AJ111">
+        <v>214</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11448,6 +11974,12 @@
       <c r="AH112">
         <v>1</v>
       </c>
+      <c r="AI112">
+        <v>298</v>
+      </c>
+      <c r="AJ112">
+        <v>284</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11560,6 +12092,12 @@
       <c r="AH113">
         <v>4</v>
       </c>
+      <c r="AI113">
+        <v>21</v>
+      </c>
+      <c r="AJ113">
+        <v>18</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11672,6 +12210,12 @@
       <c r="AH114">
         <v>4</v>
       </c>
+      <c r="AI114">
+        <v>145</v>
+      </c>
+      <c r="AJ114">
+        <v>26</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11784,6 +12328,12 @@
       <c r="AH115">
         <v>1</v>
       </c>
+      <c r="AI115">
+        <v>191</v>
+      </c>
+      <c r="AJ115">
+        <v>263</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11896,6 +12446,12 @@
       <c r="AH116">
         <v>2</v>
       </c>
+      <c r="AI116">
+        <v>63</v>
+      </c>
+      <c r="AJ116">
+        <v>207</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12008,6 +12564,12 @@
       <c r="AH117">
         <v>2</v>
       </c>
+      <c r="AI117">
+        <v>133</v>
+      </c>
+      <c r="AJ117">
+        <v>205</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12120,6 +12682,12 @@
       <c r="AH118">
         <v>3</v>
       </c>
+      <c r="AI118">
+        <v>21</v>
+      </c>
+      <c r="AJ118">
+        <v>88</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12232,6 +12800,12 @@
       <c r="AH119">
         <v>2</v>
       </c>
+      <c r="AI119">
+        <v>43</v>
+      </c>
+      <c r="AJ119">
+        <v>175</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12344,6 +12918,12 @@
       <c r="AH120">
         <v>2</v>
       </c>
+      <c r="AI120">
+        <v>141</v>
+      </c>
+      <c r="AJ120">
+        <v>181</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12456,6 +13036,12 @@
       <c r="AH121">
         <v>2</v>
       </c>
+      <c r="AI121">
+        <v>86</v>
+      </c>
+      <c r="AJ121">
+        <v>170</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12568,6 +13154,12 @@
       <c r="AH122">
         <v>4</v>
       </c>
+      <c r="AI122">
+        <v>72</v>
+      </c>
+      <c r="AJ122">
+        <v>19</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12680,6 +13272,12 @@
       <c r="AH123">
         <v>4</v>
       </c>
+      <c r="AI123">
+        <v>145</v>
+      </c>
+      <c r="AJ123">
+        <v>57</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12948,6 +13546,12 @@
       <c r="AH127">
         <v>4</v>
       </c>
+      <c r="AI127">
+        <v>125</v>
+      </c>
+      <c r="AJ127">
+        <v>71</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13060,6 +13664,12 @@
       <c r="AH128">
         <v>1</v>
       </c>
+      <c r="AI128">
+        <v>135</v>
+      </c>
+      <c r="AJ128">
+        <v>224</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13172,6 +13782,12 @@
       <c r="AH129">
         <v>4</v>
       </c>
+      <c r="AI129">
+        <v>178</v>
+      </c>
+      <c r="AJ129">
+        <v>58</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13284,6 +13900,12 @@
       <c r="AH130">
         <v>2</v>
       </c>
+      <c r="AI130">
+        <v>35</v>
+      </c>
+      <c r="AJ130">
+        <v>182</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13396,6 +14018,12 @@
       <c r="AH131">
         <v>4</v>
       </c>
+      <c r="AI131">
+        <v>175</v>
+      </c>
+      <c r="AJ131">
+        <v>30</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13508,6 +14136,12 @@
       <c r="AH132">
         <v>4</v>
       </c>
+      <c r="AI132">
+        <v>24</v>
+      </c>
+      <c r="AJ132">
+        <v>51</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13620,6 +14254,12 @@
       <c r="AH133">
         <v>3</v>
       </c>
+      <c r="AI133">
+        <v>165</v>
+      </c>
+      <c r="AJ133">
+        <v>119</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13732,6 +14372,12 @@
       <c r="AH134">
         <v>3</v>
       </c>
+      <c r="AI134">
+        <v>85</v>
+      </c>
+      <c r="AJ134">
+        <v>107</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13844,6 +14490,12 @@
       <c r="AH135">
         <v>1</v>
       </c>
+      <c r="AI135">
+        <v>286</v>
+      </c>
+      <c r="AJ135">
+        <v>243</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13956,6 +14608,12 @@
       <c r="AH136">
         <v>1</v>
       </c>
+      <c r="AI136">
+        <v>65</v>
+      </c>
+      <c r="AJ136">
+        <v>230</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14044,6 +14702,9 @@
       <c r="AH137">
         <v>1</v>
       </c>
+      <c r="AJ137">
+        <v>272</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14156,6 +14817,12 @@
       <c r="AH138">
         <v>1</v>
       </c>
+      <c r="AI138">
+        <v>139</v>
+      </c>
+      <c r="AJ138">
+        <v>231</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14268,6 +14935,12 @@
       <c r="AH139">
         <v>3</v>
       </c>
+      <c r="AI139">
+        <v>60</v>
+      </c>
+      <c r="AJ139">
+        <v>84</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14438,6 +15111,12 @@
       <c r="AH141">
         <v>1</v>
       </c>
+      <c r="AI141">
+        <v>12</v>
+      </c>
+      <c r="AJ141">
+        <v>263</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14520,6 +15199,9 @@
       <c r="X142">
         <v>2.5</v>
       </c>
+      <c r="AI142">
+        <v>293</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14632,6 +15314,12 @@
       <c r="AH143">
         <v>2</v>
       </c>
+      <c r="AI143">
+        <v>27</v>
+      </c>
+      <c r="AJ143">
+        <v>162</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14744,6 +15432,12 @@
       <c r="AH144">
         <v>4</v>
       </c>
+      <c r="AI144">
+        <v>125</v>
+      </c>
+      <c r="AJ144">
+        <v>65</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14856,6 +15550,12 @@
       <c r="AH145">
         <v>1</v>
       </c>
+      <c r="AI145">
+        <v>274</v>
+      </c>
+      <c r="AJ145">
+        <v>281</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14968,6 +15668,12 @@
       <c r="AH146">
         <v>1</v>
       </c>
+      <c r="AI146">
+        <v>278</v>
+      </c>
+      <c r="AJ146">
+        <v>273</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15080,6 +15786,12 @@
       <c r="AH147">
         <v>4</v>
       </c>
+      <c r="AI147">
+        <v>1</v>
+      </c>
+      <c r="AJ147">
+        <v>9</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15187,6 +15899,12 @@
       <c r="AH148">
         <v>2</v>
       </c>
+      <c r="AI148">
+        <v>201</v>
+      </c>
+      <c r="AJ148">
+        <v>178</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15294,6 +16012,12 @@
       <c r="AH149">
         <v>2</v>
       </c>
+      <c r="AI149">
+        <v>273</v>
+      </c>
+      <c r="AJ149">
+        <v>158</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15454,6 +16178,12 @@
       <c r="AH151">
         <v>2</v>
       </c>
+      <c r="AI151">
+        <v>239</v>
+      </c>
+      <c r="AJ151">
+        <v>208</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15561,6 +16291,12 @@
       <c r="AH152">
         <v>4</v>
       </c>
+      <c r="AI152">
+        <v>153</v>
+      </c>
+      <c r="AJ152">
+        <v>60</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15703,6 +16439,12 @@
       <c r="AH154">
         <v>3</v>
       </c>
+      <c r="AI154">
+        <v>178</v>
+      </c>
+      <c r="AJ154">
+        <v>81</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15810,6 +16552,12 @@
       <c r="AH155">
         <v>3</v>
       </c>
+      <c r="AI155">
+        <v>46</v>
+      </c>
+      <c r="AJ155">
+        <v>79</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15917,6 +16665,12 @@
       <c r="AH156">
         <v>1</v>
       </c>
+      <c r="AI156">
+        <v>228</v>
+      </c>
+      <c r="AJ156">
+        <v>223</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16024,6 +16778,12 @@
       <c r="AH157">
         <v>2</v>
       </c>
+      <c r="AI157">
+        <v>108</v>
+      </c>
+      <c r="AJ157">
+        <v>206</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16131,6 +16891,12 @@
       <c r="AH158">
         <v>1</v>
       </c>
+      <c r="AI158">
+        <v>183</v>
+      </c>
+      <c r="AJ158">
+        <v>275</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16196,6 +16962,9 @@
       <c r="AH159">
         <v>4</v>
       </c>
+      <c r="AJ159">
+        <v>70</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16279,6 +17048,9 @@
       <c r="AH160">
         <v>1</v>
       </c>
+      <c r="AJ160">
+        <v>252</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16386,6 +17158,12 @@
       <c r="AH161">
         <v>1</v>
       </c>
+      <c r="AI161">
+        <v>221</v>
+      </c>
+      <c r="AJ161">
+        <v>228</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16493,6 +17271,12 @@
       <c r="AH162">
         <v>3</v>
       </c>
+      <c r="AI162">
+        <v>33</v>
+      </c>
+      <c r="AJ162">
+        <v>92</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16570,6 +17354,9 @@
       <c r="X163">
         <v>4</v>
       </c>
+      <c r="AI163">
+        <v>194</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16677,6 +17464,12 @@
       <c r="AH164">
         <v>4</v>
       </c>
+      <c r="AI164">
+        <v>245</v>
+      </c>
+      <c r="AJ164">
+        <v>49</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16784,6 +17577,12 @@
       <c r="AH165">
         <v>2</v>
       </c>
+      <c r="AI165">
+        <v>232</v>
+      </c>
+      <c r="AJ165">
+        <v>193</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16891,6 +17690,12 @@
       <c r="AH166">
         <v>3</v>
       </c>
+      <c r="AI166">
+        <v>153</v>
+      </c>
+      <c r="AJ166">
+        <v>90</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16998,6 +17803,12 @@
       <c r="AH167">
         <v>3</v>
       </c>
+      <c r="AI167">
+        <v>122</v>
+      </c>
+      <c r="AJ167">
+        <v>80</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17105,6 +17916,12 @@
       <c r="AH168">
         <v>4</v>
       </c>
+      <c r="AI168">
+        <v>3</v>
+      </c>
+      <c r="AJ168">
+        <v>3</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17235,6 +18052,9 @@
       <c r="X170">
         <v>4</v>
       </c>
+      <c r="AI170">
+        <v>55</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17342,6 +18162,12 @@
       <c r="AH171">
         <v>4</v>
       </c>
+      <c r="AI171">
+        <v>20</v>
+      </c>
+      <c r="AJ171">
+        <v>48</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17449,6 +18275,12 @@
       <c r="AH172">
         <v>4</v>
       </c>
+      <c r="AI172">
+        <v>75</v>
+      </c>
+      <c r="AJ172">
+        <v>63</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17526,6 +18358,9 @@
       <c r="X173">
         <v>3</v>
       </c>
+      <c r="AI173">
+        <v>217</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17633,6 +18468,12 @@
       <c r="AH174">
         <v>3</v>
       </c>
+      <c r="AI174">
+        <v>193</v>
+      </c>
+      <c r="AJ174">
+        <v>97</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17740,6 +18581,12 @@
       <c r="AH175">
         <v>4</v>
       </c>
+      <c r="AI175">
+        <v>78</v>
+      </c>
+      <c r="AJ175">
+        <v>27</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17847,6 +18694,12 @@
       <c r="AH176">
         <v>3</v>
       </c>
+      <c r="AI176">
+        <v>149</v>
+      </c>
+      <c r="AJ176">
+        <v>136</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17954,6 +18807,12 @@
       <c r="AH177">
         <v>2</v>
       </c>
+      <c r="AI177">
+        <v>29</v>
+      </c>
+      <c r="AJ177">
+        <v>176</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18061,6 +18920,12 @@
       <c r="AH178">
         <v>3</v>
       </c>
+      <c r="AI178">
+        <v>155</v>
+      </c>
+      <c r="AJ178">
+        <v>115</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18168,6 +19033,12 @@
       <c r="AH179">
         <v>1</v>
       </c>
+      <c r="AI179">
+        <v>129</v>
+      </c>
+      <c r="AJ179">
+        <v>219</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18328,6 +19199,12 @@
       <c r="AH181">
         <v>1</v>
       </c>
+      <c r="AI181">
+        <v>219</v>
+      </c>
+      <c r="AJ181">
+        <v>234</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18435,6 +19312,12 @@
       <c r="AH182">
         <v>2</v>
       </c>
+      <c r="AI182">
+        <v>248</v>
+      </c>
+      <c r="AJ182">
+        <v>188</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18542,6 +19425,12 @@
       <c r="AH183">
         <v>4</v>
       </c>
+      <c r="AI183">
+        <v>98</v>
+      </c>
+      <c r="AJ183">
+        <v>41</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18702,6 +19591,12 @@
       <c r="AH185">
         <v>1</v>
       </c>
+      <c r="AI185">
+        <v>253</v>
+      </c>
+      <c r="AJ185">
+        <v>232</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -18809,6 +19704,12 @@
       <c r="AH186">
         <v>2</v>
       </c>
+      <c r="AI186">
+        <v>187</v>
+      </c>
+      <c r="AJ186">
+        <v>186</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18916,6 +19817,12 @@
       <c r="AH187">
         <v>2</v>
       </c>
+      <c r="AI187">
+        <v>159</v>
+      </c>
+      <c r="AJ187">
+        <v>213</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19023,6 +19930,12 @@
       <c r="AH188">
         <v>1</v>
       </c>
+      <c r="AI188">
+        <v>288</v>
+      </c>
+      <c r="AJ188">
+        <v>269</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19130,6 +20043,12 @@
       <c r="AH189">
         <v>2</v>
       </c>
+      <c r="AI189">
+        <v>128</v>
+      </c>
+      <c r="AJ189">
+        <v>152</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19237,6 +20156,12 @@
       <c r="AH190">
         <v>4</v>
       </c>
+      <c r="AI190">
+        <v>30</v>
+      </c>
+      <c r="AJ190">
+        <v>4</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19344,6 +20269,12 @@
       <c r="AH191">
         <v>3</v>
       </c>
+      <c r="AI191">
+        <v>238</v>
+      </c>
+      <c r="AJ191">
+        <v>139</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19451,6 +20382,12 @@
       <c r="AH192">
         <v>4</v>
       </c>
+      <c r="AI192">
+        <v>226</v>
+      </c>
+      <c r="AJ192">
+        <v>19</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19558,6 +20495,12 @@
       <c r="AH193">
         <v>1</v>
       </c>
+      <c r="AI193">
+        <v>129</v>
+      </c>
+      <c r="AJ193">
+        <v>222</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -19665,6 +20608,12 @@
       <c r="AH194">
         <v>3</v>
       </c>
+      <c r="AI194">
+        <v>183</v>
+      </c>
+      <c r="AJ194">
+        <v>139</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -19742,6 +20691,9 @@
       <c r="X195">
         <v>3.5</v>
       </c>
+      <c r="AI195">
+        <v>291</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -19849,6 +20801,12 @@
       <c r="AH196">
         <v>2</v>
       </c>
+      <c r="AI196">
+        <v>289</v>
+      </c>
+      <c r="AJ196">
+        <v>200</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19956,6 +20914,12 @@
       <c r="AH197">
         <v>1</v>
       </c>
+      <c r="AI197">
+        <v>165</v>
+      </c>
+      <c r="AJ197">
+        <v>285</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20063,6 +21027,12 @@
       <c r="AH198">
         <v>3</v>
       </c>
+      <c r="AI198">
+        <v>223</v>
+      </c>
+      <c r="AJ198">
+        <v>105</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20170,6 +21140,12 @@
       <c r="AH199">
         <v>3</v>
       </c>
+      <c r="AI199">
+        <v>90</v>
+      </c>
+      <c r="AJ199">
+        <v>135</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20277,6 +21253,12 @@
       <c r="AH200">
         <v>1</v>
       </c>
+      <c r="AI200">
+        <v>129</v>
+      </c>
+      <c r="AJ200">
+        <v>236</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20437,6 +21419,12 @@
       <c r="AH202">
         <v>2</v>
       </c>
+      <c r="AI202">
+        <v>152</v>
+      </c>
+      <c r="AJ202">
+        <v>145</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20544,6 +21532,12 @@
       <c r="AH203">
         <v>2</v>
       </c>
+      <c r="AI203">
+        <v>245</v>
+      </c>
+      <c r="AJ203">
+        <v>151</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -20651,6 +21645,12 @@
       <c r="AH204">
         <v>2</v>
       </c>
+      <c r="AI204">
+        <v>259</v>
+      </c>
+      <c r="AJ204">
+        <v>184</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -20758,6 +21758,12 @@
       <c r="AH205">
         <v>1</v>
       </c>
+      <c r="AI205">
+        <v>205</v>
+      </c>
+      <c r="AJ205">
+        <v>256</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -20865,6 +21871,12 @@
       <c r="AH206">
         <v>3</v>
       </c>
+      <c r="AI206">
+        <v>291</v>
+      </c>
+      <c r="AJ206">
+        <v>126</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -20972,6 +21984,12 @@
       <c r="AH207">
         <v>1</v>
       </c>
+      <c r="AI207">
+        <v>239</v>
+      </c>
+      <c r="AJ207">
+        <v>259</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21079,6 +22097,12 @@
       <c r="AH208">
         <v>4</v>
       </c>
+      <c r="AI208">
+        <v>4</v>
+      </c>
+      <c r="AJ208">
+        <v>2</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21186,6 +22210,12 @@
       <c r="AH209">
         <v>3</v>
       </c>
+      <c r="AI209">
+        <v>196</v>
+      </c>
+      <c r="AJ209">
+        <v>100</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21293,6 +22323,12 @@
       <c r="AH210">
         <v>3</v>
       </c>
+      <c r="AI210">
+        <v>15</v>
+      </c>
+      <c r="AJ210">
+        <v>100</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21400,6 +22436,12 @@
       <c r="AH211">
         <v>2</v>
       </c>
+      <c r="AI211">
+        <v>59</v>
+      </c>
+      <c r="AJ211">
+        <v>179</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21507,6 +22549,12 @@
       <c r="AH212">
         <v>4</v>
       </c>
+      <c r="AI212">
+        <v>158</v>
+      </c>
+      <c r="AJ212">
+        <v>12</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21614,6 +22662,12 @@
       <c r="AH213">
         <v>3</v>
       </c>
+      <c r="AI213">
+        <v>28</v>
+      </c>
+      <c r="AJ213">
+        <v>89</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -21721,6 +22775,12 @@
       <c r="AH214">
         <v>2</v>
       </c>
+      <c r="AI214">
+        <v>163</v>
+      </c>
+      <c r="AJ214">
+        <v>191</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -21828,6 +22888,12 @@
       <c r="AH215">
         <v>2</v>
       </c>
+      <c r="AI215">
+        <v>266</v>
+      </c>
+      <c r="AJ215">
+        <v>189</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -21935,6 +23001,12 @@
       <c r="AH216">
         <v>2</v>
       </c>
+      <c r="AI216">
+        <v>200</v>
+      </c>
+      <c r="AJ216">
+        <v>195</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22042,6 +23114,12 @@
       <c r="AH217">
         <v>1</v>
       </c>
+      <c r="AI217">
+        <v>264</v>
+      </c>
+      <c r="AJ217">
+        <v>262</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22149,6 +23227,12 @@
       <c r="AH218">
         <v>1</v>
       </c>
+      <c r="AI218">
+        <v>268</v>
+      </c>
+      <c r="AJ218">
+        <v>253</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22256,6 +23340,12 @@
       <c r="AH219">
         <v>3</v>
       </c>
+      <c r="AI219">
+        <v>133</v>
+      </c>
+      <c r="AJ219">
+        <v>114</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22363,6 +23453,12 @@
       <c r="AH220">
         <v>1</v>
       </c>
+      <c r="AI220">
+        <v>161</v>
+      </c>
+      <c r="AJ220">
+        <v>279</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22446,6 +23542,9 @@
       <c r="AH221">
         <v>3</v>
       </c>
+      <c r="AJ221">
+        <v>139</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22553,6 +23652,12 @@
       <c r="AH222">
         <v>1</v>
       </c>
+      <c r="AI222">
+        <v>40</v>
+      </c>
+      <c r="AJ222">
+        <v>266</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22660,6 +23765,12 @@
       <c r="AH223">
         <v>2</v>
       </c>
+      <c r="AI223">
+        <v>214</v>
+      </c>
+      <c r="AJ223">
+        <v>157</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -22767,6 +23878,12 @@
       <c r="AH224">
         <v>1</v>
       </c>
+      <c r="AI224">
+        <v>285</v>
+      </c>
+      <c r="AJ224">
+        <v>250</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -22874,6 +23991,12 @@
       <c r="AH225">
         <v>3</v>
       </c>
+      <c r="AI225">
+        <v>203</v>
+      </c>
+      <c r="AJ225">
+        <v>110</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -22981,6 +24104,12 @@
       <c r="AH226">
         <v>2</v>
       </c>
+      <c r="AI226">
+        <v>162</v>
+      </c>
+      <c r="AJ226">
+        <v>204</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -23088,6 +24217,12 @@
       <c r="AH227">
         <v>3</v>
       </c>
+      <c r="AI227">
+        <v>24</v>
+      </c>
+      <c r="AJ227">
+        <v>138</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -23195,6 +24330,12 @@
       <c r="AH228">
         <v>2</v>
       </c>
+      <c r="AI228">
+        <v>262</v>
+      </c>
+      <c r="AJ228">
+        <v>159</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -23302,6 +24443,12 @@
       <c r="AH229">
         <v>3</v>
       </c>
+      <c r="AI229">
+        <v>2</v>
+      </c>
+      <c r="AJ229">
+        <v>120</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23409,6 +24556,12 @@
       <c r="AH230">
         <v>1</v>
       </c>
+      <c r="AI230">
+        <v>115</v>
+      </c>
+      <c r="AJ230">
+        <v>254</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23516,6 +24669,12 @@
       <c r="AH231">
         <v>4</v>
       </c>
+      <c r="AI231">
+        <v>266</v>
+      </c>
+      <c r="AJ231">
+        <v>22</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23623,6 +24782,12 @@
       <c r="AH232">
         <v>1</v>
       </c>
+      <c r="AI232">
+        <v>95</v>
+      </c>
+      <c r="AJ232">
+        <v>245</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23730,6 +24895,12 @@
       <c r="AH233">
         <v>4</v>
       </c>
+      <c r="AI233">
+        <v>73</v>
+      </c>
+      <c r="AJ233">
+        <v>34</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -23837,6 +25008,12 @@
       <c r="AH234">
         <v>3</v>
       </c>
+      <c r="AI234">
+        <v>6</v>
+      </c>
+      <c r="AJ234">
+        <v>112</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -23944,6 +25121,12 @@
       <c r="AH235">
         <v>3</v>
       </c>
+      <c r="AI235">
+        <v>232</v>
+      </c>
+      <c r="AJ235">
+        <v>86</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -24042,6 +25225,9 @@
       <c r="AF236">
         <v>3</v>
       </c>
+      <c r="AI236">
+        <v>211</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24128,6 +25314,9 @@
       <c r="AH237">
         <v>1</v>
       </c>
+      <c r="AJ237">
+        <v>248</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24235,6 +25424,12 @@
       <c r="AH238">
         <v>2</v>
       </c>
+      <c r="AI238">
+        <v>129</v>
+      </c>
+      <c r="AJ238">
+        <v>208</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24342,6 +25537,12 @@
       <c r="AH239">
         <v>3</v>
       </c>
+      <c r="AI239">
+        <v>277</v>
+      </c>
+      <c r="AJ239">
+        <v>139</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -24419,6 +25620,9 @@
       <c r="X240">
         <v>2.5</v>
       </c>
+      <c r="AI240">
+        <v>281</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24496,6 +25700,9 @@
       <c r="X241">
         <v>3.5</v>
       </c>
+      <c r="AI241">
+        <v>23</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24603,6 +25810,12 @@
       <c r="AH242">
         <v>3</v>
       </c>
+      <c r="AI242">
+        <v>56</v>
+      </c>
+      <c r="AJ242">
+        <v>128</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -24710,6 +25923,12 @@
       <c r="AH243">
         <v>4</v>
       </c>
+      <c r="AI243">
+        <v>9</v>
+      </c>
+      <c r="AJ243">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -24817,6 +26036,12 @@
       <c r="AH244">
         <v>3</v>
       </c>
+      <c r="AI244">
+        <v>71</v>
+      </c>
+      <c r="AJ244">
+        <v>94</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -24924,6 +26149,12 @@
       <c r="AH245">
         <v>1</v>
       </c>
+      <c r="AI245">
+        <v>119</v>
+      </c>
+      <c r="AJ245">
+        <v>240</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -25031,6 +26262,12 @@
       <c r="AH246">
         <v>2</v>
       </c>
+      <c r="AI246">
+        <v>214</v>
+      </c>
+      <c r="AJ246">
+        <v>200</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -25138,6 +26375,12 @@
       <c r="AH247">
         <v>4</v>
       </c>
+      <c r="AI247">
+        <v>65</v>
+      </c>
+      <c r="AJ247">
+        <v>56</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25245,6 +26488,12 @@
       <c r="AH248">
         <v>1</v>
       </c>
+      <c r="AI248">
+        <v>80</v>
+      </c>
+      <c r="AJ248">
+        <v>219</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25440,6 +26689,12 @@
       <c r="AH251">
         <v>3</v>
       </c>
+      <c r="AI251">
+        <v>119</v>
+      </c>
+      <c r="AJ251">
+        <v>96</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25547,6 +26802,12 @@
       <c r="AH252">
         <v>4</v>
       </c>
+      <c r="AI252">
+        <v>101</v>
+      </c>
+      <c r="AJ252">
+        <v>72</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -25654,6 +26915,12 @@
       <c r="AH253">
         <v>2</v>
       </c>
+      <c r="AI253">
+        <v>135</v>
+      </c>
+      <c r="AJ253">
+        <v>196</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -25761,6 +27028,12 @@
       <c r="AH254">
         <v>4</v>
       </c>
+      <c r="AI254">
+        <v>18</v>
+      </c>
+      <c r="AJ254">
+        <v>33</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -25868,6 +27141,12 @@
       <c r="AH255">
         <v>2</v>
       </c>
+      <c r="AI255">
+        <v>214</v>
+      </c>
+      <c r="AJ255">
+        <v>208</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -25975,6 +27254,12 @@
       <c r="AH256">
         <v>2</v>
       </c>
+      <c r="AI256">
+        <v>145</v>
+      </c>
+      <c r="AJ256">
+        <v>199</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -26082,6 +27367,12 @@
       <c r="AH257">
         <v>4</v>
       </c>
+      <c r="AI257">
+        <v>11</v>
+      </c>
+      <c r="AJ257">
+        <v>15</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -26165,6 +27456,9 @@
       <c r="AH258">
         <v>4</v>
       </c>
+      <c r="AJ258">
+        <v>8</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -26272,6 +27566,12 @@
       <c r="AH259">
         <v>3</v>
       </c>
+      <c r="AI259">
+        <v>208</v>
+      </c>
+      <c r="AJ259">
+        <v>139</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -26379,6 +27679,12 @@
       <c r="AH260">
         <v>4</v>
       </c>
+      <c r="AI260">
+        <v>70</v>
+      </c>
+      <c r="AJ260">
+        <v>44</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -26465,6 +27771,9 @@
       <c r="AH261">
         <v>4</v>
       </c>
+      <c r="AJ261">
+        <v>7</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26572,6 +27881,12 @@
       <c r="AH262">
         <v>4</v>
       </c>
+      <c r="AI262">
+        <v>43</v>
+      </c>
+      <c r="AJ262">
+        <v>66</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -26679,6 +27994,12 @@
       <c r="AH263">
         <v>2</v>
       </c>
+      <c r="AI263">
+        <v>65</v>
+      </c>
+      <c r="AJ263">
+        <v>208</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -26786,6 +28107,12 @@
       <c r="AH264">
         <v>3</v>
       </c>
+      <c r="AI264">
+        <v>148</v>
+      </c>
+      <c r="AJ264">
+        <v>76</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -26893,6 +28220,12 @@
       <c r="AH265">
         <v>4</v>
       </c>
+      <c r="AI265">
+        <v>50</v>
+      </c>
+      <c r="AJ265">
+        <v>55</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -27000,6 +28333,12 @@
       <c r="AH266">
         <v>3</v>
       </c>
+      <c r="AI266">
+        <v>8</v>
+      </c>
+      <c r="AJ266">
+        <v>116</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -27107,6 +28446,12 @@
       <c r="AH267">
         <v>4</v>
       </c>
+      <c r="AI267">
+        <v>36</v>
+      </c>
+      <c r="AJ267">
+        <v>49</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -27214,6 +28559,12 @@
       <c r="AH268">
         <v>4</v>
       </c>
+      <c r="AI268">
+        <v>186</v>
+      </c>
+      <c r="AJ268">
+        <v>54</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -27321,6 +28672,12 @@
       <c r="AH269">
         <v>4</v>
       </c>
+      <c r="AI269">
+        <v>278</v>
+      </c>
+      <c r="AJ269">
+        <v>45</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -27428,6 +28785,12 @@
       <c r="AH270">
         <v>2</v>
       </c>
+      <c r="AI270">
+        <v>198</v>
+      </c>
+      <c r="AJ270">
+        <v>159</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27535,6 +28898,12 @@
       <c r="AH271">
         <v>4</v>
       </c>
+      <c r="AI271">
+        <v>10</v>
+      </c>
+      <c r="AJ271">
+        <v>14</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27642,6 +29011,12 @@
       <c r="AH272">
         <v>3</v>
       </c>
+      <c r="AI272">
+        <v>83</v>
+      </c>
+      <c r="AJ272">
+        <v>100</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -27802,6 +29177,12 @@
       <c r="AH274">
         <v>4</v>
       </c>
+      <c r="AI274">
+        <v>37</v>
+      </c>
+      <c r="AJ274">
+        <v>42</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -27909,6 +29290,12 @@
       <c r="AH275">
         <v>1</v>
       </c>
+      <c r="AI275">
+        <v>222</v>
+      </c>
+      <c r="AJ275">
+        <v>239</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -28016,6 +29403,12 @@
       <c r="AH276">
         <v>2</v>
       </c>
+      <c r="AI276">
+        <v>137</v>
+      </c>
+      <c r="AJ276">
+        <v>155</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -28123,6 +29516,12 @@
       <c r="AH277">
         <v>3</v>
       </c>
+      <c r="AI277">
+        <v>102</v>
+      </c>
+      <c r="AJ277">
+        <v>132</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28230,6 +29629,12 @@
       <c r="AH278">
         <v>1</v>
       </c>
+      <c r="AI278">
+        <v>183</v>
+      </c>
+      <c r="AJ278">
+        <v>235</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -28337,6 +29742,12 @@
       <c r="AH279">
         <v>4</v>
       </c>
+      <c r="AI279">
+        <v>13</v>
+      </c>
+      <c r="AJ279">
+        <v>11</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -28444,6 +29855,12 @@
       <c r="AH280">
         <v>1</v>
       </c>
+      <c r="AI280">
+        <v>301</v>
+      </c>
+      <c r="AJ280">
+        <v>287</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28551,6 +29968,12 @@
       <c r="AH281">
         <v>3</v>
       </c>
+      <c r="AI281">
+        <v>211</v>
+      </c>
+      <c r="AJ281">
+        <v>120</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28658,6 +30081,12 @@
       <c r="AH282">
         <v>2</v>
       </c>
+      <c r="AI282">
+        <v>108</v>
+      </c>
+      <c r="AJ282">
+        <v>148</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -28765,6 +30194,12 @@
       <c r="AH283">
         <v>2</v>
       </c>
+      <c r="AI283">
+        <v>175</v>
+      </c>
+      <c r="AJ283">
+        <v>194</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -28872,6 +30307,12 @@
       <c r="AH284">
         <v>4</v>
       </c>
+      <c r="AI284">
+        <v>49</v>
+      </c>
+      <c r="AJ284">
+        <v>25</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -28979,6 +30420,12 @@
       <c r="AH285">
         <v>1</v>
       </c>
+      <c r="AI285">
+        <v>151</v>
+      </c>
+      <c r="AJ285">
+        <v>283</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -29086,6 +30533,12 @@
       <c r="AH286">
         <v>1</v>
       </c>
+      <c r="AI286">
+        <v>231</v>
+      </c>
+      <c r="AJ286">
+        <v>240</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -29193,6 +30646,12 @@
       <c r="AH287">
         <v>3</v>
       </c>
+      <c r="AI287">
+        <v>118</v>
+      </c>
+      <c r="AJ287">
+        <v>85</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -29300,6 +30759,12 @@
       <c r="AH288">
         <v>1</v>
       </c>
+      <c r="AI288">
+        <v>79</v>
+      </c>
+      <c r="AJ288">
+        <v>233</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -29407,6 +30872,12 @@
       <c r="AH289">
         <v>4</v>
       </c>
+      <c r="AI289">
+        <v>115</v>
+      </c>
+      <c r="AJ289">
+        <v>68</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -29514,6 +30985,12 @@
       <c r="AH290">
         <v>4</v>
       </c>
+      <c r="AI290">
+        <v>45</v>
+      </c>
+      <c r="AJ290">
+        <v>64</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29621,6 +31098,12 @@
       <c r="AH291">
         <v>2</v>
       </c>
+      <c r="AI291">
+        <v>169</v>
+      </c>
+      <c r="AJ291">
+        <v>147</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29728,6 +31211,12 @@
       <c r="AH292">
         <v>4</v>
       </c>
+      <c r="AI292">
+        <v>68</v>
+      </c>
+      <c r="AJ292">
+        <v>28</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -29835,6 +31324,12 @@
       <c r="AH293">
         <v>2</v>
       </c>
+      <c r="AI293">
+        <v>52</v>
+      </c>
+      <c r="AJ293">
+        <v>173</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -29942,6 +31437,12 @@
       <c r="AH294">
         <v>4</v>
       </c>
+      <c r="AI294">
+        <v>52</v>
+      </c>
+      <c r="AJ294">
+        <v>10</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -30049,6 +31550,12 @@
       <c r="AH295">
         <v>4</v>
       </c>
+      <c r="AI295">
+        <v>105</v>
+      </c>
+      <c r="AJ295">
+        <v>29</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -30156,6 +31663,12 @@
       <c r="AH296">
         <v>4</v>
       </c>
+      <c r="AI296">
+        <v>37</v>
+      </c>
+      <c r="AJ296">
+        <v>59</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -30263,6 +31776,12 @@
       <c r="AH297">
         <v>1</v>
       </c>
+      <c r="AI297">
+        <v>19</v>
+      </c>
+      <c r="AJ297">
+        <v>226</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -30370,6 +31889,12 @@
       <c r="AH298">
         <v>1</v>
       </c>
+      <c r="AI298">
+        <v>74</v>
+      </c>
+      <c r="AJ298">
+        <v>217</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -30477,6 +32002,12 @@
       <c r="AH299">
         <v>3</v>
       </c>
+      <c r="AI299">
+        <v>86</v>
+      </c>
+      <c r="AJ299">
+        <v>109</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -30575,6 +32106,9 @@
       <c r="AF300">
         <v>3</v>
       </c>
+      <c r="AI300">
+        <v>297</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -30682,6 +32216,12 @@
       <c r="AH301">
         <v>4</v>
       </c>
+      <c r="AI301">
+        <v>48</v>
+      </c>
+      <c r="AJ301">
+        <v>37</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30789,6 +32329,12 @@
       <c r="AH302">
         <v>1</v>
       </c>
+      <c r="AI302">
+        <v>7</v>
+      </c>
+      <c r="AJ302">
+        <v>248</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -30896,6 +32442,12 @@
       <c r="AH303">
         <v>1</v>
       </c>
+      <c r="AI303">
+        <v>270</v>
+      </c>
+      <c r="AJ303">
+        <v>221</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -31003,6 +32555,12 @@
       <c r="AH304">
         <v>3</v>
       </c>
+      <c r="AI304">
+        <v>187</v>
+      </c>
+      <c r="AJ304">
+        <v>144</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -31110,6 +32668,12 @@
       <c r="AH305">
         <v>3</v>
       </c>
+      <c r="AI305">
+        <v>83</v>
+      </c>
+      <c r="AJ305">
+        <v>131</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -31217,6 +32781,12 @@
       <c r="AH306">
         <v>2</v>
       </c>
+      <c r="AI306">
+        <v>60</v>
+      </c>
+      <c r="AJ306">
+        <v>203</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -31324,6 +32894,12 @@
       <c r="AH307">
         <v>2</v>
       </c>
+      <c r="AI307">
+        <v>119</v>
+      </c>
+      <c r="AJ307">
+        <v>153</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -31484,6 +33060,12 @@
       <c r="AH309">
         <v>3</v>
       </c>
+      <c r="AI309">
+        <v>113</v>
+      </c>
+      <c r="AJ309">
+        <v>118</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -31644,6 +33226,12 @@
       <c r="AH311">
         <v>2</v>
       </c>
+      <c r="AI311">
+        <v>80</v>
+      </c>
+      <c r="AJ311">
+        <v>153</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -31751,6 +33339,12 @@
       <c r="AH312">
         <v>2</v>
       </c>
+      <c r="AI312">
+        <v>282</v>
+      </c>
+      <c r="AJ312">
+        <v>187</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -31858,6 +33452,12 @@
       <c r="AH313">
         <v>3</v>
       </c>
+      <c r="AI313">
+        <v>198</v>
+      </c>
+      <c r="AJ313">
+        <v>77</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -31935,6 +33535,9 @@
       <c r="X314">
         <v>3</v>
       </c>
+      <c r="AI314">
+        <v>294</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -32042,6 +33645,12 @@
       <c r="AH315">
         <v>3</v>
       </c>
+      <c r="AI315">
+        <v>156</v>
+      </c>
+      <c r="AJ315">
+        <v>137</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -32149,6 +33758,12 @@
       <c r="AH316">
         <v>1</v>
       </c>
+      <c r="AI316">
+        <v>171</v>
+      </c>
+      <c r="AJ316">
+        <v>255</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -32256,6 +33871,12 @@
       <c r="AH317">
         <v>4</v>
       </c>
+      <c r="AI317">
+        <v>5</v>
+      </c>
+      <c r="AJ317">
+        <v>24</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -32363,6 +33984,12 @@
       <c r="AH318">
         <v>1</v>
       </c>
+      <c r="AI318">
+        <v>149</v>
+      </c>
+      <c r="AJ318">
+        <v>273</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -32470,6 +34097,12 @@
       <c r="AH319">
         <v>1</v>
       </c>
+      <c r="AI319">
+        <v>236</v>
+      </c>
+      <c r="AJ319">
+        <v>277</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -32577,6 +34210,12 @@
       <c r="AH320">
         <v>1</v>
       </c>
+      <c r="AI320">
+        <v>14</v>
+      </c>
+      <c r="AJ320">
+        <v>247</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -32684,6 +34323,12 @@
       <c r="AH321">
         <v>1</v>
       </c>
+      <c r="AI321">
+        <v>167</v>
+      </c>
+      <c r="AJ321">
+        <v>266</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -32791,6 +34436,12 @@
       <c r="AH322">
         <v>3</v>
       </c>
+      <c r="AI322">
+        <v>75</v>
+      </c>
+      <c r="AJ322">
+        <v>129</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -32898,6 +34549,12 @@
       <c r="AH323">
         <v>2</v>
       </c>
+      <c r="AI323">
+        <v>86</v>
+      </c>
+      <c r="AJ323">
+        <v>172</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -33005,6 +34662,12 @@
       <c r="AH324">
         <v>1</v>
       </c>
+      <c r="AI324">
+        <v>103</v>
+      </c>
+      <c r="AJ324">
+        <v>285</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -33112,6 +34775,12 @@
       <c r="AH325">
         <v>3</v>
       </c>
+      <c r="AI325">
+        <v>168</v>
+      </c>
+      <c r="AJ325">
+        <v>100</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -33219,6 +34888,12 @@
       <c r="AH326">
         <v>2</v>
       </c>
+      <c r="AI326">
+        <v>141</v>
+      </c>
+      <c r="AJ326">
+        <v>190</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -33326,6 +35001,12 @@
       <c r="AH327">
         <v>1</v>
       </c>
+      <c r="AI327">
+        <v>141</v>
+      </c>
+      <c r="AJ327">
+        <v>276</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -33433,6 +35114,12 @@
       <c r="AH328">
         <v>3</v>
       </c>
+      <c r="AI328">
+        <v>90</v>
+      </c>
+      <c r="AJ328">
+        <v>93</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -33540,6 +35227,12 @@
       <c r="AH329">
         <v>2</v>
       </c>
+      <c r="AI329">
+        <v>227</v>
+      </c>
+      <c r="AJ329">
+        <v>183</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -33638,6 +35331,9 @@
       <c r="AF330">
         <v>1</v>
       </c>
+      <c r="AI330">
+        <v>58</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -33798,6 +35494,12 @@
       <c r="AH332">
         <v>1</v>
       </c>
+      <c r="AI332">
+        <v>105</v>
+      </c>
+      <c r="AJ332">
+        <v>279</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -33905,6 +35607,12 @@
       <c r="AH333">
         <v>3</v>
       </c>
+      <c r="AI333">
+        <v>206</v>
+      </c>
+      <c r="AJ333">
+        <v>134</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -34012,6 +35720,12 @@
       <c r="AH334">
         <v>2</v>
       </c>
+      <c r="AI334">
+        <v>213</v>
+      </c>
+      <c r="AJ334">
+        <v>149</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -34119,6 +35833,12 @@
       <c r="AH335">
         <v>1</v>
       </c>
+      <c r="AI335">
+        <v>201</v>
+      </c>
+      <c r="AJ335">
+        <v>260</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -34226,6 +35946,12 @@
       <c r="AH336">
         <v>4</v>
       </c>
+      <c r="AI336">
+        <v>95</v>
+      </c>
+      <c r="AJ336">
+        <v>21</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -34333,6 +36059,12 @@
       <c r="AH337">
         <v>3</v>
       </c>
+      <c r="AI337">
+        <v>75</v>
+      </c>
+      <c r="AJ337">
+        <v>95</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -34440,6 +36172,12 @@
       <c r="AH338">
         <v>1</v>
       </c>
+      <c r="AI338">
+        <v>229</v>
+      </c>
+      <c r="AJ338">
+        <v>238</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -34600,6 +36338,12 @@
       <c r="AH340">
         <v>1</v>
       </c>
+      <c r="AI340">
+        <v>32</v>
+      </c>
+      <c r="AJ340">
+        <v>261</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -34677,6 +36421,9 @@
       <c r="X341">
         <v>3.333333333333333</v>
       </c>
+      <c r="AI341">
+        <v>39</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -34784,6 +36531,12 @@
       <c r="AH342">
         <v>1</v>
       </c>
+      <c r="AI342">
+        <v>232</v>
+      </c>
+      <c r="AJ342">
+        <v>251</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -34891,6 +36644,12 @@
       <c r="AH343">
         <v>1</v>
       </c>
+      <c r="AI343">
+        <v>173</v>
+      </c>
+      <c r="AJ343">
+        <v>225</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -34998,6 +36757,12 @@
       <c r="AH344">
         <v>1</v>
       </c>
+      <c r="AI344">
+        <v>248</v>
+      </c>
+      <c r="AJ344">
+        <v>245</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -35105,6 +36870,12 @@
       <c r="AH345">
         <v>4</v>
       </c>
+      <c r="AI345">
+        <v>34</v>
+      </c>
+      <c r="AJ345">
+        <v>5</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -35211,6 +36982,12 @@
       </c>
       <c r="AH346">
         <v>4</v>
+      </c>
+      <c r="AI346">
+        <v>68</v>
+      </c>
+      <c r="AJ346">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/proc_data/private_data/2025_c_educativo.xlsx
+++ b/data/proc_data/private_data/2025_c_educativo.xlsx
@@ -642,7 +642,7 @@
         <v>2</v>
       </c>
       <c r="AG2">
-        <v>0.5268335577959018</v>
+        <v>0.527</v>
       </c>
       <c r="AH2">
         <v>3</v>
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
       <c r="AG3">
-        <v>0.2840198990005576</v>
+        <v>0.284</v>
       </c>
       <c r="AH3">
         <v>1</v>
@@ -936,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="AG5">
-        <v>0.4650402373198379</v>
+        <v>0.465</v>
       </c>
       <c r="AH5">
         <v>2</v>
@@ -1054,7 +1054,7 @@
         <v>2</v>
       </c>
       <c r="AG6">
-        <v>0.3807224227512509</v>
+        <v>0.381</v>
       </c>
       <c r="AH6">
         <v>1</v>
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="AG7">
-        <v>0.5468749408319875</v>
+        <v>0.547</v>
       </c>
       <c r="AH7">
         <v>3</v>
@@ -1290,7 +1290,7 @@
         <v>2</v>
       </c>
       <c r="AG8">
-        <v>0.5322230432940037</v>
+        <v>0.532</v>
       </c>
       <c r="AH8">
         <v>3</v>
@@ -1408,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="AG9">
-        <v>0.09867339514506224</v>
+        <v>0.099</v>
       </c>
       <c r="AH9">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>2</v>
       </c>
       <c r="AG10">
-        <v>0.5033197334174075</v>
+        <v>0.503</v>
       </c>
       <c r="AH10">
         <v>2</v>
@@ -1644,7 +1644,7 @@
         <v>2</v>
       </c>
       <c r="AG11">
-        <v>0.4227532582376633</v>
+        <v>0.423</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -1762,7 +1762,7 @@
         <v>2</v>
       </c>
       <c r="AG12">
-        <v>0.4327816681081055</v>
+        <v>0.433</v>
       </c>
       <c r="AH12">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>2</v>
       </c>
       <c r="AG13">
-        <v>0.4432432905372893</v>
+        <v>0.443</v>
       </c>
       <c r="AH13">
         <v>1</v>
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="AG14">
-        <v>0.3243126172300133</v>
+        <v>0.324</v>
       </c>
       <c r="AH14">
         <v>1</v>
@@ -2326,7 +2326,7 @@
         <v>2</v>
       </c>
       <c r="AG18">
-        <v>0.4788754843582047</v>
+        <v>0.479</v>
       </c>
       <c r="AH18">
         <v>2</v>
@@ -2550,7 +2550,7 @@
         <v>3</v>
       </c>
       <c r="AG20">
-        <v>0.5913190300305384</v>
+        <v>0.591</v>
       </c>
       <c r="AH20">
         <v>4</v>
@@ -2668,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="AG21">
-        <v>0.5037745101440905</v>
+        <v>0.504</v>
       </c>
       <c r="AH21">
         <v>2</v>
@@ -2871,7 +2871,7 @@
         <v>2</v>
       </c>
       <c r="AG23">
-        <v>0.5077929320306707</v>
+        <v>0.508</v>
       </c>
       <c r="AH23">
         <v>2</v>
@@ -2989,7 +2989,7 @@
         <v>3</v>
       </c>
       <c r="AG24">
-        <v>0.5522082315358137</v>
+        <v>0.552</v>
       </c>
       <c r="AH24">
         <v>3</v>
@@ -3107,7 +3107,7 @@
         <v>2</v>
       </c>
       <c r="AG25">
-        <v>0.5427724095213521</v>
+        <v>0.543</v>
       </c>
       <c r="AH25">
         <v>3</v>
@@ -3429,7 +3429,7 @@
         <v>3</v>
       </c>
       <c r="AG29">
-        <v>0.3807224227512509</v>
+        <v>0.381</v>
       </c>
       <c r="AH29">
         <v>1</v>
@@ -3708,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="AG32">
-        <v>0.4646457619465154</v>
+        <v>0.465</v>
       </c>
       <c r="AH32">
         <v>2</v>
@@ -3826,7 +3826,7 @@
         <v>3</v>
       </c>
       <c r="AG33">
-        <v>0.6117340072667959</v>
+        <v>0.612</v>
       </c>
       <c r="AH33">
         <v>4</v>
@@ -3944,7 +3944,7 @@
         <v>3</v>
       </c>
       <c r="AG34">
-        <v>0.5384272553912703</v>
+        <v>0.538</v>
       </c>
       <c r="AH34">
         <v>3</v>
@@ -4084,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="AG36">
-        <v>0.536162775743106</v>
+        <v>0.536</v>
       </c>
       <c r="AH36">
         <v>3</v>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
       <c r="AG37">
-        <v>0.6496091624024841</v>
+        <v>0.65</v>
       </c>
       <c r="AH37">
         <v>4</v>
@@ -4378,7 +4378,7 @@
         <v>2</v>
       </c>
       <c r="AG39">
-        <v>0.5386698782107167</v>
+        <v>0.539</v>
       </c>
       <c r="AH39">
         <v>3</v>
@@ -4594,7 +4594,7 @@
         <v>2</v>
       </c>
       <c r="AG42">
-        <v>0.5587266979516011</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AH42">
         <v>4</v>
@@ -4770,7 +4770,7 @@
         <v>2</v>
       </c>
       <c r="AG44">
-        <v>0.47890324757345</v>
+        <v>0.479</v>
       </c>
       <c r="AH44">
         <v>2</v>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="AG49">
-        <v>0.5988403374333702</v>
+        <v>0.599</v>
       </c>
       <c r="AH49">
         <v>4</v>
@@ -5210,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="AG52">
-        <v>0.4446535356753204</v>
+        <v>0.445</v>
       </c>
       <c r="AH52">
         <v>1</v>
@@ -5350,7 +5350,7 @@
         <v>2</v>
       </c>
       <c r="AG54">
-        <v>0.4780926544040323</v>
+        <v>0.478</v>
       </c>
       <c r="AH54">
         <v>2</v>
@@ -5468,7 +5468,7 @@
         <v>2</v>
       </c>
       <c r="AG55">
-        <v>0.5206724640682264</v>
+        <v>0.521</v>
       </c>
       <c r="AH55">
         <v>3</v>
@@ -5586,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AG56">
-        <v>0.5667722176885696</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AH56">
         <v>4</v>
@@ -5704,7 +5704,7 @@
         <v>2</v>
       </c>
       <c r="AG57">
-        <v>0.5269092884535616</v>
+        <v>0.527</v>
       </c>
       <c r="AH57">
         <v>3</v>
@@ -5822,7 +5822,7 @@
         <v>2</v>
       </c>
       <c r="AG58">
-        <v>0.4996958307596797</v>
+        <v>0.5</v>
       </c>
       <c r="AH58">
         <v>2</v>
@@ -5940,7 +5940,7 @@
         <v>2</v>
       </c>
       <c r="AG59">
-        <v>0.4677422002607572</v>
+        <v>0.468</v>
       </c>
       <c r="AH59">
         <v>2</v>
@@ -6058,7 +6058,7 @@
         <v>3</v>
       </c>
       <c r="AG60">
-        <v>0.5965697540664776</v>
+        <v>0.597</v>
       </c>
       <c r="AH60">
         <v>4</v>
@@ -6176,7 +6176,7 @@
         <v>3</v>
       </c>
       <c r="AG61">
-        <v>0.5834843348192554</v>
+        <v>0.583</v>
       </c>
       <c r="AH61">
         <v>4</v>
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="AG62">
-        <v>0.5527915165997067</v>
+        <v>0.553</v>
       </c>
       <c r="AH62">
         <v>3</v>
@@ -6412,7 +6412,7 @@
         <v>3</v>
       </c>
       <c r="AG63">
-        <v>0.5302492840531985</v>
+        <v>0.53</v>
       </c>
       <c r="AH63">
         <v>3</v>
@@ -6530,7 +6530,7 @@
         <v>3</v>
       </c>
       <c r="AG64">
-        <v>0.6003681029995703</v>
+        <v>0.6</v>
       </c>
       <c r="AH64">
         <v>4</v>
@@ -6648,7 +6648,7 @@
         <v>3</v>
       </c>
       <c r="AG65">
-        <v>0.5485463424770612</v>
+        <v>0.549</v>
       </c>
       <c r="AH65">
         <v>3</v>
@@ -6766,7 +6766,7 @@
         <v>3</v>
       </c>
       <c r="AG66">
-        <v>0.5250375085430841</v>
+        <v>0.525</v>
       </c>
       <c r="AH66">
         <v>3</v>
@@ -6884,7 +6884,7 @@
         <v>3</v>
       </c>
       <c r="AG67">
-        <v>0.5649775523062393</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AH67">
         <v>4</v>
@@ -7002,7 +7002,7 @@
         <v>3</v>
       </c>
       <c r="AG68">
-        <v>0.5530914676344948</v>
+        <v>0.553</v>
       </c>
       <c r="AH68">
         <v>3</v>
@@ -7120,7 +7120,7 @@
         <v>2</v>
       </c>
       <c r="AG69">
-        <v>0.4854834901478353</v>
+        <v>0.485</v>
       </c>
       <c r="AH69">
         <v>2</v>
@@ -7238,7 +7238,7 @@
         <v>2</v>
       </c>
       <c r="AG70">
-        <v>0.4998097899627528</v>
+        <v>0.5</v>
       </c>
       <c r="AH70">
         <v>2</v>
@@ -7356,7 +7356,7 @@
         <v>2</v>
       </c>
       <c r="AG71">
-        <v>0.4896517023784687</v>
+        <v>0.49</v>
       </c>
       <c r="AH71">
         <v>2</v>
@@ -7474,7 +7474,7 @@
         <v>2</v>
       </c>
       <c r="AG72">
-        <v>0.497003827598341</v>
+        <v>0.497</v>
       </c>
       <c r="AH72">
         <v>2</v>
@@ -7592,7 +7592,7 @@
         <v>2</v>
       </c>
       <c r="AG73">
-        <v>0.4985321319744513</v>
+        <v>0.499</v>
       </c>
       <c r="AH73">
         <v>2</v>
@@ -7710,7 +7710,7 @@
         <v>3</v>
       </c>
       <c r="AG74">
-        <v>0.6315801461280494</v>
+        <v>0.632</v>
       </c>
       <c r="AH74">
         <v>4</v>
@@ -7828,7 +7828,7 @@
         <v>2</v>
       </c>
       <c r="AG75">
-        <v>0.493351620948085</v>
+        <v>0.493</v>
       </c>
       <c r="AH75">
         <v>2</v>
@@ -7946,7 +7946,7 @@
         <v>3</v>
       </c>
       <c r="AG76">
-        <v>0.5260172115517473</v>
+        <v>0.526</v>
       </c>
       <c r="AH76">
         <v>3</v>
@@ -8064,7 +8064,7 @@
         <v>2</v>
       </c>
       <c r="AG77">
-        <v>0.5390086758414747</v>
+        <v>0.539</v>
       </c>
       <c r="AH77">
         <v>3</v>
@@ -8182,7 +8182,7 @@
         <v>3</v>
       </c>
       <c r="AG78">
-        <v>0.5330085698007473</v>
+        <v>0.533</v>
       </c>
       <c r="AH78">
         <v>3</v>
@@ -8300,7 +8300,7 @@
         <v>2</v>
       </c>
       <c r="AG79">
-        <v>0.511469533630613</v>
+        <v>0.511</v>
       </c>
       <c r="AH79">
         <v>2</v>
@@ -8418,7 +8418,7 @@
         <v>3</v>
       </c>
       <c r="AG80">
-        <v>0.5754572629334775</v>
+        <v>0.575</v>
       </c>
       <c r="AH80">
         <v>4</v>
@@ -8536,7 +8536,7 @@
         <v>2</v>
       </c>
       <c r="AG81">
-        <v>0.4584425992471785</v>
+        <v>0.458</v>
       </c>
       <c r="AH81">
         <v>1</v>
@@ -8654,7 +8654,7 @@
         <v>2</v>
       </c>
       <c r="AG82">
-        <v>0.4241145808445107</v>
+        <v>0.424</v>
       </c>
       <c r="AH82">
         <v>1</v>
@@ -8772,7 +8772,7 @@
         <v>3</v>
       </c>
       <c r="AG83">
-        <v>0.5221808581352779</v>
+        <v>0.522</v>
       </c>
       <c r="AH83">
         <v>3</v>
@@ -8890,7 +8890,7 @@
         <v>3</v>
       </c>
       <c r="AG84">
-        <v>0.6970841734400132</v>
+        <v>0.697</v>
       </c>
       <c r="AH84">
         <v>4</v>
@@ -9008,7 +9008,7 @@
         <v>3</v>
       </c>
       <c r="AG85">
-        <v>0.5466379959543105</v>
+        <v>0.547</v>
       </c>
       <c r="AH85">
         <v>3</v>
@@ -9126,7 +9126,7 @@
         <v>2</v>
       </c>
       <c r="AG86">
-        <v>0.5127504679674463</v>
+        <v>0.513</v>
       </c>
       <c r="AH86">
         <v>2</v>
@@ -9244,7 +9244,7 @@
         <v>3</v>
       </c>
       <c r="AG87">
-        <v>0.5950796837319542</v>
+        <v>0.595</v>
       </c>
       <c r="AH87">
         <v>4</v>
@@ -9362,7 +9362,7 @@
         <v>3</v>
       </c>
       <c r="AG88">
-        <v>0.502943668047266</v>
+        <v>0.503</v>
       </c>
       <c r="AH88">
         <v>2</v>
@@ -9480,7 +9480,7 @@
         <v>3</v>
       </c>
       <c r="AG89">
-        <v>0.5569041004340289</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AH89">
         <v>4</v>
@@ -9598,7 +9598,7 @@
         <v>3</v>
       </c>
       <c r="AG90">
-        <v>0.5262483250757369</v>
+        <v>0.526</v>
       </c>
       <c r="AH90">
         <v>3</v>
@@ -9716,7 +9716,7 @@
         <v>2</v>
       </c>
       <c r="AG91">
-        <v>0.2378175820974486</v>
+        <v>0.238</v>
       </c>
       <c r="AH91">
         <v>1</v>
@@ -9834,7 +9834,7 @@
         <v>3</v>
       </c>
       <c r="AG92">
-        <v>0.5355253768106627</v>
+        <v>0.536</v>
       </c>
       <c r="AH92">
         <v>3</v>
@@ -9952,7 +9952,7 @@
         <v>2</v>
       </c>
       <c r="AG93">
-        <v>0.4957614359781685</v>
+        <v>0.496</v>
       </c>
       <c r="AH93">
         <v>2</v>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="AG94">
-        <v>0.4980548182354254</v>
+        <v>0.498</v>
       </c>
       <c r="AH94">
         <v>2</v>
@@ -10188,7 +10188,7 @@
         <v>3</v>
       </c>
       <c r="AG95">
-        <v>0.5758339853776496</v>
+        <v>0.576</v>
       </c>
       <c r="AH95">
         <v>4</v>
@@ -10306,7 +10306,7 @@
         <v>3</v>
       </c>
       <c r="AG96">
-        <v>0.5450629895031235</v>
+        <v>0.545</v>
       </c>
       <c r="AH96">
         <v>3</v>
@@ -10424,7 +10424,7 @@
         <v>2</v>
       </c>
       <c r="AG97">
-        <v>0.3355945783342608</v>
+        <v>0.336</v>
       </c>
       <c r="AH97">
         <v>1</v>
@@ -10542,7 +10542,7 @@
         <v>3</v>
       </c>
       <c r="AG98">
-        <v>0.5966913924611325</v>
+        <v>0.597</v>
       </c>
       <c r="AH98">
         <v>4</v>
@@ -10851,7 +10851,7 @@
         <v>3</v>
       </c>
       <c r="AG101">
-        <v>0.5817920406536182</v>
+        <v>0.582</v>
       </c>
       <c r="AH101">
         <v>4</v>
@@ -10969,7 +10969,7 @@
         <v>3</v>
       </c>
       <c r="AG102">
-        <v>0.5003112104562749</v>
+        <v>0.5</v>
       </c>
       <c r="AH102">
         <v>2</v>
@@ -11087,7 +11087,7 @@
         <v>2</v>
       </c>
       <c r="AG103">
-        <v>0.3280732709314291</v>
+        <v>0.328</v>
       </c>
       <c r="AH103">
         <v>1</v>
@@ -11205,7 +11205,7 @@
         <v>3</v>
       </c>
       <c r="AG104">
-        <v>0.6214042596418652</v>
+        <v>0.621</v>
       </c>
       <c r="AH104">
         <v>4</v>
@@ -11323,7 +11323,7 @@
         <v>3</v>
       </c>
       <c r="AG105">
-        <v>0.5883105070694057</v>
+        <v>0.588</v>
       </c>
       <c r="AH105">
         <v>4</v>
@@ -11441,7 +11441,7 @@
         <v>3</v>
       </c>
       <c r="AG106">
-        <v>0.500484779088648</v>
+        <v>0.5</v>
       </c>
       <c r="AH106">
         <v>2</v>
@@ -11733,7 +11733,7 @@
         <v>2</v>
       </c>
       <c r="AG110">
-        <v>0.3468765394385083</v>
+        <v>0.347</v>
       </c>
       <c r="AH110">
         <v>1</v>
@@ -11851,7 +11851,7 @@
         <v>2</v>
       </c>
       <c r="AG111">
-        <v>0.4650955247897204</v>
+        <v>0.465</v>
       </c>
       <c r="AH111">
         <v>2</v>
@@ -11969,7 +11969,7 @@
         <v>3</v>
       </c>
       <c r="AG112">
-        <v>0.2227749672917853</v>
+        <v>0.223</v>
       </c>
       <c r="AH112">
         <v>1</v>
@@ -12087,7 +12087,7 @@
         <v>3</v>
       </c>
       <c r="AG113">
-        <v>0.6188971571742546</v>
+        <v>0.619</v>
       </c>
       <c r="AH113">
         <v>4</v>
@@ -12205,7 +12205,7 @@
         <v>3</v>
       </c>
       <c r="AG114">
-        <v>0.605287172350083</v>
+        <v>0.605</v>
       </c>
       <c r="AH114">
         <v>4</v>
@@ -12323,7 +12323,7 @@
         <v>2</v>
       </c>
       <c r="AG115">
-        <v>0.3468765394385083</v>
+        <v>0.347</v>
       </c>
       <c r="AH115">
         <v>1</v>
@@ -12441,7 +12441,7 @@
         <v>2</v>
       </c>
       <c r="AG116">
-        <v>0.4721352358010515</v>
+        <v>0.472</v>
       </c>
       <c r="AH116">
         <v>2</v>
@@ -12559,7 +12559,7 @@
         <v>2</v>
       </c>
       <c r="AG117">
-        <v>0.473029377240549</v>
+        <v>0.473</v>
       </c>
       <c r="AH117">
         <v>2</v>
@@ -12677,7 +12677,7 @@
         <v>2</v>
       </c>
       <c r="AG118">
-        <v>0.5449877764290951</v>
+        <v>0.545</v>
       </c>
       <c r="AH118">
         <v>3</v>
@@ -12795,7 +12795,7 @@
         <v>3</v>
       </c>
       <c r="AG119">
-        <v>0.4968326057824652</v>
+        <v>0.497</v>
       </c>
       <c r="AH119">
         <v>2</v>
@@ -12913,7 +12913,7 @@
         <v>2</v>
       </c>
       <c r="AG120">
-        <v>0.491166884087569</v>
+        <v>0.491</v>
       </c>
       <c r="AH120">
         <v>2</v>
@@ -13031,7 +13031,7 @@
         <v>3</v>
       </c>
       <c r="AG121">
-        <v>0.4980548182354254</v>
+        <v>0.498</v>
       </c>
       <c r="AH121">
         <v>2</v>
@@ -13149,7 +13149,7 @@
         <v>3</v>
       </c>
       <c r="AG122">
-        <v>0.6176436059404494</v>
+        <v>0.618</v>
       </c>
       <c r="AH122">
         <v>4</v>
@@ -13267,7 +13267,7 @@
         <v>3</v>
       </c>
       <c r="AG123">
-        <v>0.5723310746157028</v>
+        <v>0.572</v>
       </c>
       <c r="AH123">
         <v>4</v>
@@ -13541,7 +13541,7 @@
         <v>3</v>
       </c>
       <c r="AG127">
-        <v>0.5555148339608372</v>
+        <v>0.556</v>
       </c>
       <c r="AH127">
         <v>4</v>
@@ -13659,7 +13659,7 @@
         <v>2</v>
       </c>
       <c r="AG128">
-        <v>0.4478356272688261</v>
+        <v>0.448</v>
       </c>
       <c r="AH128">
         <v>1</v>
@@ -13777,7 +13777,7 @@
         <v>3</v>
       </c>
       <c r="AG129">
-        <v>0.5709040527942809</v>
+        <v>0.571</v>
       </c>
       <c r="AH129">
         <v>4</v>
@@ -13895,7 +13895,7 @@
         <v>2</v>
       </c>
       <c r="AG130">
-        <v>0.490887454710374</v>
+        <v>0.491</v>
       </c>
       <c r="AH130">
         <v>2</v>
@@ -14013,7 +14013,7 @@
         <v>3</v>
       </c>
       <c r="AG131">
-        <v>0.6007206642840781</v>
+        <v>0.601</v>
       </c>
       <c r="AH131">
         <v>4</v>
@@ -14131,7 +14131,7 @@
         <v>3</v>
       </c>
       <c r="AG132">
-        <v>0.5773508877109939</v>
+        <v>0.577</v>
       </c>
       <c r="AH132">
         <v>4</v>
@@ -14249,7 +14249,7 @@
         <v>2</v>
       </c>
       <c r="AG133">
-        <v>0.5286414683402744</v>
+        <v>0.529</v>
       </c>
       <c r="AH133">
         <v>3</v>
@@ -14367,7 +14367,7 @@
         <v>3</v>
       </c>
       <c r="AG134">
-        <v>0.5360152991273642</v>
+        <v>0.536</v>
       </c>
       <c r="AH134">
         <v>3</v>
@@ -14485,7 +14485,7 @@
         <v>2</v>
       </c>
       <c r="AG135">
-        <v>0.4235938749473915</v>
+        <v>0.424</v>
       </c>
       <c r="AH135">
         <v>1</v>
@@ -14603,7 +14603,7 @@
         <v>2</v>
       </c>
       <c r="AG136">
-        <v>0.4419673544600234</v>
+        <v>0.442</v>
       </c>
       <c r="AH136">
         <v>1</v>
@@ -14697,7 +14697,7 @@
         <v>2</v>
       </c>
       <c r="AG137">
-        <v>0.3205519635285974</v>
+        <v>0.321</v>
       </c>
       <c r="AH137">
         <v>1</v>
@@ -14812,7 +14812,7 @@
         <v>2</v>
       </c>
       <c r="AG138">
-        <v>0.4403556457308451</v>
+        <v>0.44</v>
       </c>
       <c r="AH138">
         <v>1</v>
@@ -14930,7 +14930,7 @@
         <v>2</v>
       </c>
       <c r="AG139">
-        <v>0.5461911856135482</v>
+        <v>0.546</v>
       </c>
       <c r="AH139">
         <v>3</v>
@@ -15106,7 +15106,7 @@
         <v>2</v>
       </c>
       <c r="AG141">
-        <v>0.3468765394385083</v>
+        <v>0.347</v>
       </c>
       <c r="AH141">
         <v>1</v>
@@ -15309,7 +15309,7 @@
         <v>2</v>
       </c>
       <c r="AG143">
-        <v>0.5034854571398429</v>
+        <v>0.503</v>
       </c>
       <c r="AH143">
         <v>2</v>
@@ -15427,7 +15427,7 @@
         <v>3</v>
       </c>
       <c r="AG144">
-        <v>0.5612338004192117</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AH144">
         <v>4</v>
@@ -15545,7 +15545,7 @@
         <v>2</v>
       </c>
       <c r="AG145">
-        <v>0.2679028117087754</v>
+        <v>0.268</v>
       </c>
       <c r="AH145">
         <v>1</v>
@@ -15663,7 +15663,7 @@
         <v>2</v>
       </c>
       <c r="AG146">
-        <v>0.3017486950215181</v>
+        <v>0.302</v>
       </c>
       <c r="AH146">
         <v>1</v>
@@ -15781,7 +15781,7 @@
         <v>3</v>
       </c>
       <c r="AG147">
-        <v>0.6633652377839789</v>
+        <v>0.663</v>
       </c>
       <c r="AH147">
         <v>4</v>
@@ -15894,7 +15894,7 @@
         <v>2</v>
       </c>
       <c r="AG148">
-        <v>0.4945043874117284</v>
+        <v>0.495</v>
       </c>
       <c r="AH148">
         <v>2</v>
@@ -16007,7 +16007,7 @@
         <v>2</v>
       </c>
       <c r="AG149">
-        <v>0.5053145149459847</v>
+        <v>0.505</v>
       </c>
       <c r="AH149">
         <v>2</v>
@@ -16173,7 +16173,7 @@
         <v>2</v>
       </c>
       <c r="AG151">
-        <v>0.4709781115852312</v>
+        <v>0.471</v>
       </c>
       <c r="AH151">
         <v>2</v>
@@ -16286,7 +16286,7 @@
         <v>3</v>
       </c>
       <c r="AG152">
-        <v>0.5675419937248124</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AH152">
         <v>4</v>
@@ -16434,7 +16434,7 @@
         <v>3</v>
       </c>
       <c r="AG154">
-        <v>0.5476954470941146</v>
+        <v>0.548</v>
       </c>
       <c r="AH154">
         <v>3</v>
@@ -16547,7 +16547,7 @@
         <v>2</v>
       </c>
       <c r="AG155">
-        <v>0.5481083816181916</v>
+        <v>0.548</v>
       </c>
       <c r="AH155">
         <v>3</v>
@@ -16660,7 +16660,7 @@
         <v>3</v>
       </c>
       <c r="AG156">
-        <v>0.4525167206873717</v>
+        <v>0.453</v>
       </c>
       <c r="AH156">
         <v>1</v>
@@ -16773,7 +16773,7 @@
         <v>2</v>
       </c>
       <c r="AG157">
-        <v>0.4724284085283783</v>
+        <v>0.472</v>
       </c>
       <c r="AH157">
         <v>2</v>
@@ -16886,7 +16886,7 @@
         <v>2</v>
       </c>
       <c r="AG158">
-        <v>0.2944780978654475</v>
+        <v>0.294</v>
       </c>
       <c r="AH158">
         <v>1</v>
@@ -16957,7 +16957,7 @@
         <v>3</v>
       </c>
       <c r="AG159">
-        <v>0.555592819867088</v>
+        <v>0.556</v>
       </c>
       <c r="AH159">
         <v>4</v>
@@ -17043,7 +17043,7 @@
         <v>2</v>
       </c>
       <c r="AG160">
-        <v>0.3965171682971974</v>
+        <v>0.397</v>
       </c>
       <c r="AH160">
         <v>1</v>
@@ -17153,7 +17153,7 @@
         <v>3</v>
       </c>
       <c r="AG161">
-        <v>0.4434783313936279</v>
+        <v>0.443</v>
       </c>
       <c r="AH161">
         <v>1</v>
@@ -17266,7 +17266,7 @@
         <v>2</v>
       </c>
       <c r="AG162">
-        <v>0.5411313969970978</v>
+        <v>0.541</v>
       </c>
       <c r="AH162">
         <v>3</v>
@@ -17459,7 +17459,7 @@
         <v>3</v>
       </c>
       <c r="AG164">
-        <v>0.578156742075583</v>
+        <v>0.578</v>
       </c>
       <c r="AH164">
         <v>4</v>
@@ -17572,7 +17572,7 @@
         <v>2</v>
       </c>
       <c r="AG165">
-        <v>0.4836703178275098</v>
+        <v>0.484</v>
       </c>
       <c r="AH165">
         <v>2</v>
@@ -17685,7 +17685,7 @@
         <v>3</v>
       </c>
       <c r="AG166">
-        <v>0.5434743635478867</v>
+        <v>0.543</v>
       </c>
       <c r="AH166">
         <v>3</v>
@@ -17798,7 +17798,7 @@
         <v>3</v>
       </c>
       <c r="AG167">
-        <v>0.5477929455234106</v>
+        <v>0.548</v>
       </c>
       <c r="AH167">
         <v>3</v>
@@ -17911,7 +17911,7 @@
         <v>3</v>
       </c>
       <c r="AG168">
-        <v>0.7229419095800932</v>
+        <v>0.723</v>
       </c>
       <c r="AH168">
         <v>4</v>
@@ -18157,7 +18157,7 @@
         <v>3</v>
       </c>
       <c r="AG171">
-        <v>0.5791522092318401</v>
+        <v>0.579</v>
       </c>
       <c r="AH171">
         <v>4</v>
@@ -18270,7 +18270,7 @@
         <v>2</v>
       </c>
       <c r="AG172">
-        <v>0.5635480488508522</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AH172">
         <v>4</v>
@@ -18463,7 +18463,7 @@
         <v>3</v>
       </c>
       <c r="AG174">
-        <v>0.5406319584027596</v>
+        <v>0.541</v>
       </c>
       <c r="AH174">
         <v>3</v>
@@ -18576,7 +18576,7 @@
         <v>3</v>
       </c>
       <c r="AG175">
-        <v>0.6050343552945256</v>
+        <v>0.605</v>
       </c>
       <c r="AH175">
         <v>4</v>
@@ -18689,7 +18689,7 @@
         <v>2</v>
       </c>
       <c r="AG176">
-        <v>0.5175616929188986</v>
+        <v>0.518</v>
       </c>
       <c r="AH176">
         <v>3</v>
@@ -18802,7 +18802,7 @@
         <v>2</v>
       </c>
       <c r="AG177">
-        <v>0.4963625240697882</v>
+        <v>0.496</v>
       </c>
       <c r="AH177">
         <v>2</v>
@@ -18915,7 +18915,7 @@
         <v>3</v>
       </c>
       <c r="AG178">
-        <v>0.5314494231039981</v>
+        <v>0.531</v>
       </c>
       <c r="AH178">
         <v>3</v>
@@ -19028,7 +19028,7 @@
         <v>2</v>
       </c>
       <c r="AG179">
-        <v>0.4559354967795679</v>
+        <v>0.456</v>
       </c>
       <c r="AH179">
         <v>1</v>
@@ -19194,7 +19194,7 @@
         <v>2</v>
       </c>
       <c r="AG181">
-        <v>0.4385049983648937</v>
+        <v>0.439</v>
       </c>
       <c r="AH181">
         <v>1</v>
@@ -19307,7 +19307,7 @@
         <v>2</v>
       </c>
       <c r="AG182">
-        <v>0.4879010532416027</v>
+        <v>0.488</v>
       </c>
       <c r="AH182">
         <v>2</v>
@@ -19420,7 +19420,7 @@
         <v>3</v>
       </c>
       <c r="AG183">
-        <v>0.5911590022134569</v>
+        <v>0.591</v>
       </c>
       <c r="AH183">
         <v>4</v>
@@ -19586,7 +19586,7 @@
         <v>2</v>
       </c>
       <c r="AG185">
-        <v>0.4387439370016669</v>
+        <v>0.439</v>
       </c>
       <c r="AH185">
         <v>1</v>
@@ -19699,7 +19699,7 @@
         <v>2</v>
       </c>
       <c r="AG186">
-        <v>0.4890762575232951</v>
+        <v>0.489</v>
       </c>
       <c r="AH186">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         <v>2</v>
       </c>
       <c r="AG187">
-        <v>0.4663267767440064</v>
+        <v>0.466</v>
       </c>
       <c r="AH187">
         <v>2</v>
@@ -19925,7 +19925,7 @@
         <v>1</v>
       </c>
       <c r="AG188">
-        <v>0.3310817938925618</v>
+        <v>0.331</v>
       </c>
       <c r="AH188">
         <v>1</v>
@@ -20038,7 +20038,7 @@
         <v>2</v>
       </c>
       <c r="AG189">
-        <v>0.5093801714977663</v>
+        <v>0.509</v>
       </c>
       <c r="AH189">
         <v>2</v>
@@ -20151,7 +20151,7 @@
         <v>4</v>
       </c>
       <c r="AG190">
-        <v>0.7191812558786774</v>
+        <v>0.719</v>
       </c>
       <c r="AH190">
         <v>4</v>
@@ -20264,7 +20264,7 @@
         <v>3</v>
       </c>
       <c r="AG191">
-        <v>0.5161059560022214</v>
+        <v>0.516</v>
       </c>
       <c r="AH191">
         <v>3</v>
@@ -20377,7 +20377,7 @@
         <v>3</v>
       </c>
       <c r="AG192">
-        <v>0.6176436059404494</v>
+        <v>0.618</v>
       </c>
       <c r="AH192">
         <v>4</v>
@@ -20490,7 +20490,7 @@
         <v>2</v>
       </c>
       <c r="AG193">
-        <v>0.4529725574996645</v>
+        <v>0.453</v>
       </c>
       <c r="AH193">
         <v>1</v>
@@ -20603,7 +20603,7 @@
         <v>3</v>
       </c>
       <c r="AG194">
-        <v>0.5161059560022214</v>
+        <v>0.516</v>
       </c>
       <c r="AH194">
         <v>3</v>
@@ -20796,7 +20796,7 @@
         <v>3</v>
       </c>
       <c r="AG196">
-        <v>0.478499418988063</v>
+        <v>0.478</v>
       </c>
       <c r="AH196">
         <v>2</v>
@@ -20909,7 +20909,7 @@
         <v>1</v>
       </c>
       <c r="AG197">
-        <v>0.1325192784578049</v>
+        <v>0.133</v>
       </c>
       <c r="AH197">
         <v>1</v>
@@ -21022,7 +21022,7 @@
         <v>3</v>
       </c>
       <c r="AG198">
-        <v>0.5363299159076134</v>
+        <v>0.536</v>
       </c>
       <c r="AH198">
         <v>3</v>
@@ -21135,7 +21135,7 @@
         <v>2</v>
       </c>
       <c r="AG199">
-        <v>0.5195601860687072</v>
+        <v>0.52</v>
       </c>
       <c r="AH199">
         <v>3</v>
@@ -21248,7 +21248,7 @@
         <v>2</v>
       </c>
       <c r="AG200">
-        <v>0.4355205195433104</v>
+        <v>0.436</v>
       </c>
       <c r="AH200">
         <v>1</v>
@@ -21414,7 +21414,7 @@
         <v>3</v>
       </c>
       <c r="AG202">
-        <v>0.5130290575192449</v>
+        <v>0.513</v>
       </c>
       <c r="AH202">
         <v>2</v>
@@ -21527,7 +21527,7 @@
         <v>2</v>
       </c>
       <c r="AG203">
-        <v>0.5094695082938405</v>
+        <v>0.509</v>
       </c>
       <c r="AH203">
         <v>2</v>
@@ -21640,7 +21640,7 @@
         <v>2</v>
       </c>
       <c r="AG204">
-        <v>0.4897813800923105</v>
+        <v>0.49</v>
       </c>
       <c r="AH204">
         <v>2</v>
@@ -21753,7 +21753,7 @@
         <v>2</v>
       </c>
       <c r="AG205">
-        <v>0.3841937953987117</v>
+        <v>0.384</v>
       </c>
       <c r="AH205">
         <v>1</v>
@@ -21866,7 +21866,7 @@
         <v>2</v>
       </c>
       <c r="AG206">
-        <v>0.5251315248856195</v>
+        <v>0.525</v>
       </c>
       <c r="AH206">
         <v>3</v>
@@ -21979,7 +21979,7 @@
         <v>2</v>
       </c>
       <c r="AG207">
-        <v>0.3762096383095519</v>
+        <v>0.376</v>
       </c>
       <c r="AH207">
         <v>1</v>
@@ -22092,7 +22092,7 @@
         <v>3</v>
       </c>
       <c r="AG208">
-        <v>0.7236940403203763</v>
+        <v>0.724</v>
       </c>
       <c r="AH208">
         <v>4</v>
@@ -22205,7 +22205,7 @@
         <v>2</v>
       </c>
       <c r="AG209">
-        <v>0.5386698782107165</v>
+        <v>0.539</v>
       </c>
       <c r="AH209">
         <v>3</v>
@@ -22318,7 +22318,7 @@
         <v>3</v>
       </c>
       <c r="AG210">
-        <v>0.5386698782107165</v>
+        <v>0.539</v>
       </c>
       <c r="AH210">
         <v>3</v>
@@ -22431,7 +22431,7 @@
         <v>2</v>
       </c>
       <c r="AG211">
-        <v>0.4935420337937264</v>
+        <v>0.494</v>
       </c>
       <c r="AH211">
         <v>2</v>
@@ -22544,7 +22544,7 @@
         <v>3</v>
       </c>
       <c r="AG212">
-        <v>0.6514894892531921</v>
+        <v>0.651</v>
       </c>
       <c r="AH212">
         <v>4</v>
@@ -22657,7 +22657,7 @@
         <v>3</v>
       </c>
       <c r="AG213">
-        <v>0.5443108587628404</v>
+        <v>0.544</v>
       </c>
       <c r="AH213">
         <v>3</v>
@@ -22770,7 +22770,7 @@
         <v>2</v>
       </c>
       <c r="AG214">
-        <v>0.4860207263908947</v>
+        <v>0.486</v>
       </c>
       <c r="AH214">
         <v>2</v>
@@ -22883,7 +22883,7 @@
         <v>2</v>
       </c>
       <c r="AG215">
-        <v>0.4864594693227265</v>
+        <v>0.486</v>
       </c>
       <c r="AH215">
         <v>2</v>
@@ -22996,7 +22996,7 @@
         <v>2</v>
       </c>
       <c r="AG216">
-        <v>0.4810065214556736</v>
+        <v>0.481</v>
       </c>
       <c r="AH216">
         <v>2</v>
@@ -23109,7 +23109,7 @@
         <v>2</v>
       </c>
       <c r="AG217">
-        <v>0.3678287529178251</v>
+        <v>0.368</v>
       </c>
       <c r="AH217">
         <v>1</v>
@@ -23222,7 +23222,7 @@
         <v>2</v>
       </c>
       <c r="AG218">
-        <v>0.3950337993371946</v>
+        <v>0.395</v>
       </c>
       <c r="AH218">
         <v>1</v>
@@ -23335,7 +23335,7 @@
         <v>3</v>
       </c>
       <c r="AG219">
-        <v>0.5315318221405132</v>
+        <v>0.532</v>
       </c>
       <c r="AH219">
         <v>3</v>
@@ -23448,7 +23448,7 @@
         <v>1</v>
       </c>
       <c r="AG220">
-        <v>0.2829454265144389</v>
+        <v>0.283</v>
       </c>
       <c r="AH220">
         <v>1</v>
@@ -23537,7 +23537,7 @@
         <v>3</v>
       </c>
       <c r="AG221">
-        <v>0.5161059560022214</v>
+        <v>0.516</v>
       </c>
       <c r="AH221">
         <v>3</v>
@@ -23647,7 +23647,7 @@
         <v>1</v>
       </c>
       <c r="AG222">
-        <v>0.3355945783342608</v>
+        <v>0.336</v>
       </c>
       <c r="AH222">
         <v>1</v>
@@ -23760,7 +23760,7 @@
         <v>2</v>
       </c>
       <c r="AG223">
-        <v>0.5058496277256328</v>
+        <v>0.506</v>
       </c>
       <c r="AH223">
         <v>2</v>
@@ -23873,7 +23873,7 @@
         <v>2</v>
       </c>
       <c r="AG224">
-        <v>0.3995256912583302</v>
+        <v>0.4</v>
       </c>
       <c r="AH224">
         <v>1</v>
@@ -23986,7 +23986,7 @@
         <v>2</v>
       </c>
       <c r="AG225">
-        <v>0.5341570937690175</v>
+        <v>0.534</v>
       </c>
       <c r="AH225">
         <v>3</v>
@@ -24099,7 +24099,7 @@
         <v>2</v>
       </c>
       <c r="AG226">
-        <v>0.4758833120653389</v>
+        <v>0.476</v>
       </c>
       <c r="AH226">
         <v>2</v>
@@ -24212,7 +24212,7 @@
         <v>3</v>
       </c>
       <c r="AG227">
-        <v>0.5161059560022215</v>
+        <v>0.516</v>
       </c>
       <c r="AH227">
         <v>3</v>
@@ -24325,7 +24325,7 @@
         <v>2</v>
       </c>
       <c r="AG228">
-        <v>0.5048239948979739</v>
+        <v>0.505</v>
       </c>
       <c r="AH228">
         <v>2</v>
@@ -24438,7 +24438,7 @@
         <v>3</v>
       </c>
       <c r="AG229">
-        <v>0.527387917106469</v>
+        <v>0.527</v>
       </c>
       <c r="AH229">
         <v>3</v>
@@ -24551,7 +24551,7 @@
         <v>2</v>
       </c>
       <c r="AG230">
-        <v>0.3920043838554984</v>
+        <v>0.392</v>
       </c>
       <c r="AH230">
         <v>1</v>
@@ -24664,7 +24664,7 @@
         <v>3</v>
       </c>
       <c r="AG231">
-        <v>0.6138829522390336</v>
+        <v>0.614</v>
       </c>
       <c r="AH231">
         <v>4</v>
@@ -24777,7 +24777,7 @@
         <v>2</v>
       </c>
       <c r="AG232">
-        <v>0.4168246982848431</v>
+        <v>0.417</v>
       </c>
       <c r="AH232">
         <v>1</v>
@@ -24890,7 +24890,7 @@
         <v>3</v>
       </c>
       <c r="AG233">
-        <v>0.5972687209611367</v>
+        <v>0.597</v>
       </c>
       <c r="AH233">
         <v>4</v>
@@ -25003,7 +25003,7 @@
         <v>2</v>
       </c>
       <c r="AG234">
-        <v>0.5322230432940037</v>
+        <v>0.532</v>
       </c>
       <c r="AH234">
         <v>3</v>
@@ -25116,7 +25116,7 @@
         <v>3</v>
       </c>
       <c r="AG235">
-        <v>0.5455698602194013</v>
+        <v>0.546</v>
       </c>
       <c r="AH235">
         <v>3</v>
@@ -25309,7 +25309,7 @@
         <v>2</v>
       </c>
       <c r="AG237">
-        <v>0.4032863449597461</v>
+        <v>0.403</v>
       </c>
       <c r="AH237">
         <v>1</v>
@@ -25419,7 +25419,7 @@
         <v>2</v>
       </c>
       <c r="AG238">
-        <v>0.4709781115852312</v>
+        <v>0.471</v>
       </c>
       <c r="AH238">
         <v>2</v>
@@ -25532,7 +25532,7 @@
         <v>3</v>
       </c>
       <c r="AG239">
-        <v>0.5161059560022214</v>
+        <v>0.516</v>
       </c>
       <c r="AH239">
         <v>3</v>
@@ -25805,7 +25805,7 @@
         <v>3</v>
       </c>
       <c r="AG242">
-        <v>0.5247801645397937</v>
+        <v>0.525</v>
       </c>
       <c r="AH242">
         <v>3</v>
@@ -25918,7 +25918,7 @@
         <v>3</v>
       </c>
       <c r="AG243">
-        <v>0.7417451780871724</v>
+        <v>0.742</v>
       </c>
       <c r="AH243">
         <v>4</v>
@@ -26031,7 +26031,7 @@
         <v>2</v>
       </c>
       <c r="AG244">
-        <v>0.5408820274468435</v>
+        <v>0.541</v>
       </c>
       <c r="AH244">
         <v>3</v>
@@ -26144,7 +26144,7 @@
         <v>2</v>
       </c>
       <c r="AG245">
-        <v>0.425850267168241</v>
+        <v>0.426</v>
       </c>
       <c r="AH245">
         <v>1</v>
@@ -26257,7 +26257,7 @@
         <v>2</v>
       </c>
       <c r="AG246">
-        <v>0.478499418988063</v>
+        <v>0.478</v>
       </c>
       <c r="AH246">
         <v>2</v>
@@ -26370,7 +26370,7 @@
         <v>2</v>
       </c>
       <c r="AG247">
-        <v>0.5725157615234592</v>
+        <v>0.573</v>
       </c>
       <c r="AH247">
         <v>4</v>
@@ -26483,7 +26483,7 @@
         <v>2</v>
       </c>
       <c r="AG248">
-        <v>0.4559354967795679</v>
+        <v>0.456</v>
       </c>
       <c r="AH248">
         <v>1</v>
@@ -26684,7 +26684,7 @@
         <v>2</v>
       </c>
       <c r="AG251">
-        <v>0.5407211438660343</v>
+        <v>0.541</v>
       </c>
       <c r="AH251">
         <v>3</v>
@@ -26797,7 +26797,7 @@
         <v>3</v>
       </c>
       <c r="AG252">
-        <v>0.5538448327360779</v>
+        <v>0.554</v>
       </c>
       <c r="AH252">
         <v>4</v>
@@ -26910,7 +26910,7 @@
         <v>2</v>
       </c>
       <c r="AG253">
-        <v>0.4808498275514478</v>
+        <v>0.481</v>
       </c>
       <c r="AH253">
         <v>2</v>
@@ -27023,7 +27023,7 @@
         <v>3</v>
       </c>
       <c r="AG254">
-        <v>0.5973360759528039</v>
+        <v>0.597</v>
       </c>
       <c r="AH254">
         <v>4</v>
@@ -27136,7 +27136,7 @@
         <v>2</v>
       </c>
       <c r="AG255">
-        <v>0.4709781115852312</v>
+        <v>0.471</v>
       </c>
       <c r="AH255">
         <v>2</v>
@@ -27249,7 +27249,7 @@
         <v>3</v>
       </c>
       <c r="AG256">
-        <v>0.4788128067965143</v>
+        <v>0.479</v>
       </c>
       <c r="AH256">
         <v>2</v>
@@ -27362,7 +27362,7 @@
         <v>3</v>
       </c>
       <c r="AG257">
-        <v>0.6439681818503604</v>
+        <v>0.644</v>
       </c>
       <c r="AH257">
         <v>4</v>
@@ -27451,7 +27451,7 @@
         <v>3</v>
       </c>
       <c r="AG258">
-        <v>0.6740534114616871</v>
+        <v>0.674</v>
       </c>
       <c r="AH258">
         <v>4</v>
@@ -27561,7 +27561,7 @@
         <v>2</v>
       </c>
       <c r="AG259">
-        <v>0.5161059560022214</v>
+        <v>0.516</v>
       </c>
       <c r="AH259">
         <v>3</v>
@@ -27674,7 +27674,7 @@
         <v>3</v>
       </c>
       <c r="AG260">
-        <v>0.5870211400860632</v>
+        <v>0.587</v>
       </c>
       <c r="AH260">
         <v>4</v>
@@ -27766,7 +27766,7 @@
         <v>4</v>
       </c>
       <c r="AG261">
-        <v>0.6921045492284832</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AH261">
         <v>4</v>
@@ -27876,7 +27876,7 @@
         <v>3</v>
       </c>
       <c r="AG262">
-        <v>0.5609067870538712</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AH262">
         <v>4</v>
@@ -27989,7 +27989,7 @@
         <v>3</v>
       </c>
       <c r="AG263">
-        <v>0.4709781115852312</v>
+        <v>0.471</v>
       </c>
       <c r="AH263">
         <v>2</v>
@@ -28102,7 +28102,7 @@
         <v>3</v>
       </c>
       <c r="AG264">
-        <v>0.5499518393149642</v>
+        <v>0.55</v>
       </c>
       <c r="AH264">
         <v>3</v>
@@ -28215,7 +28215,7 @@
         <v>3</v>
       </c>
       <c r="AG265">
-        <v>0.5734051053041994</v>
+        <v>0.573</v>
       </c>
       <c r="AH265">
         <v>4</v>
@@ -28328,7 +28328,7 @@
         <v>3</v>
       </c>
       <c r="AG266">
-        <v>0.5311485708078849</v>
+        <v>0.531</v>
       </c>
       <c r="AH266">
         <v>3</v>
@@ -28441,7 +28441,7 @@
         <v>3</v>
       </c>
       <c r="AG267">
-        <v>0.578156742075583</v>
+        <v>0.578</v>
       </c>
       <c r="AH267">
         <v>4</v>
@@ -28554,7 +28554,7 @@
         <v>3</v>
       </c>
       <c r="AG268">
-        <v>0.5747721537443087</v>
+        <v>0.575</v>
       </c>
       <c r="AH268">
         <v>4</v>
@@ -28667,7 +28667,7 @@
         <v>3</v>
       </c>
       <c r="AG269">
-        <v>0.5837977226277067</v>
+        <v>0.584</v>
       </c>
       <c r="AH269">
         <v>4</v>
@@ -28780,7 +28780,7 @@
         <v>3</v>
       </c>
       <c r="AG270">
-        <v>0.5048239948979739</v>
+        <v>0.505</v>
       </c>
       <c r="AH270">
         <v>2</v>
@@ -28893,7 +28893,7 @@
         <v>3</v>
       </c>
       <c r="AG271">
-        <v>0.6458485087010682</v>
+        <v>0.646</v>
       </c>
       <c r="AH271">
         <v>4</v>
@@ -29006,7 +29006,7 @@
         <v>3</v>
       </c>
       <c r="AG272">
-        <v>0.5386698782107165</v>
+        <v>0.539</v>
       </c>
       <c r="AH272">
         <v>3</v>
@@ -29172,7 +29172,7 @@
         <v>3</v>
       </c>
       <c r="AG274">
-        <v>0.5904985237684114</v>
+        <v>0.59</v>
       </c>
       <c r="AH274">
         <v>4</v>
@@ -29285,7 +29285,7 @@
         <v>2</v>
       </c>
       <c r="AG275">
-        <v>0.4290736846265976</v>
+        <v>0.429</v>
       </c>
       <c r="AH275">
         <v>1</v>
@@ -29398,7 +29398,7 @@
         <v>3</v>
       </c>
       <c r="AG276">
-        <v>0.5077929320306707</v>
+        <v>0.508</v>
       </c>
       <c r="AH276">
         <v>2</v>
@@ -29511,7 +29511,7 @@
         <v>3</v>
       </c>
       <c r="AG277">
-        <v>0.5213868739659119</v>
+        <v>0.521</v>
       </c>
       <c r="AH277">
         <v>3</v>
@@ -29624,7 +29624,7 @@
         <v>2</v>
       </c>
       <c r="AG278">
-        <v>0.4361065954448298</v>
+        <v>0.436</v>
       </c>
       <c r="AH278">
         <v>1</v>
@@ -29737,7 +29737,7 @@
         <v>3</v>
       </c>
       <c r="AG279">
-        <v>0.6518719286126581</v>
+        <v>0.652</v>
       </c>
       <c r="AH279">
         <v>4</v>
@@ -29850,7 +29850,7 @@
         <v>1</v>
       </c>
       <c r="AG280">
-        <v>0.1144681406910089</v>
+        <v>0.114</v>
       </c>
       <c r="AH280">
         <v>1</v>
@@ -29963,7 +29963,7 @@
         <v>3</v>
       </c>
       <c r="AG281">
-        <v>0.527387917106469</v>
+        <v>0.527</v>
       </c>
       <c r="AH281">
         <v>3</v>
@@ -30076,7 +30076,7 @@
         <v>2</v>
       </c>
       <c r="AG282">
-        <v>0.5123453023008055</v>
+        <v>0.512</v>
       </c>
       <c r="AH282">
         <v>2</v>
@@ -30189,7 +30189,7 @@
         <v>2</v>
       </c>
       <c r="AG283">
-        <v>0.481607397253696</v>
+        <v>0.482</v>
       </c>
       <c r="AH283">
         <v>2</v>
@@ -30302,7 +30302,7 @@
         <v>3</v>
       </c>
       <c r="AG284">
-        <v>0.60682449452253</v>
+        <v>0.607</v>
       </c>
       <c r="AH284">
         <v>4</v>
@@ -30415,7 +30415,7 @@
         <v>2</v>
       </c>
       <c r="AG285">
-        <v>0.2302962746946169</v>
+        <v>0.23</v>
       </c>
       <c r="AH285">
         <v>1</v>
@@ -30528,7 +30528,7 @@
         <v>2</v>
       </c>
       <c r="AG286">
-        <v>0.425850267168241</v>
+        <v>0.426</v>
       </c>
       <c r="AH286">
         <v>1</v>
@@ -30641,7 +30641,7 @@
         <v>3</v>
       </c>
       <c r="AG287">
-        <v>0.5455830799086385</v>
+        <v>0.546</v>
       </c>
       <c r="AH287">
         <v>3</v>
@@ -30754,7 +30754,7 @@
         <v>2</v>
       </c>
       <c r="AG288">
-        <v>0.4385786335422641</v>
+        <v>0.439</v>
       </c>
       <c r="AH288">
         <v>1</v>
@@ -30867,7 +30867,7 @@
         <v>3</v>
       </c>
       <c r="AG289">
-        <v>0.5572224364710348</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AH289">
         <v>4</v>
@@ -30980,7 +30980,7 @@
         <v>2</v>
       </c>
       <c r="AG290">
-        <v>0.5631141272699196</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AH290">
         <v>4</v>
@@ -31093,7 +31093,7 @@
         <v>3</v>
       </c>
       <c r="AG291">
-        <v>0.5124681994805905</v>
+        <v>0.512</v>
       </c>
       <c r="AH291">
         <v>2</v>
@@ -31206,7 +31206,7 @@
         <v>3</v>
       </c>
       <c r="AG292">
-        <v>0.6038545423685913</v>
+        <v>0.604</v>
       </c>
       <c r="AH292">
         <v>4</v>
@@ -31319,7 +31319,7 @@
         <v>2</v>
       </c>
       <c r="AG293">
-        <v>0.4974698276596495</v>
+        <v>0.497</v>
       </c>
       <c r="AH293">
         <v>2</v>
@@ -31432,7 +31432,7 @@
         <v>3</v>
       </c>
       <c r="AG294">
-        <v>0.6560858437771447</v>
+        <v>0.656</v>
       </c>
       <c r="AH294">
         <v>4</v>
@@ -31545,7 +31545,7 @@
         <v>3</v>
       </c>
       <c r="AG295">
-        <v>0.6030710728474631</v>
+        <v>0.603</v>
       </c>
       <c r="AH295">
         <v>4</v>
@@ -31658,7 +31658,7 @@
         <v>3</v>
       </c>
       <c r="AG296">
-        <v>0.5682850261093664</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AH296">
         <v>4</v>
@@ -31771,7 +31771,7 @@
         <v>2</v>
       </c>
       <c r="AG297">
-        <v>0.4446535356753204</v>
+        <v>0.445</v>
       </c>
       <c r="AH297">
         <v>1</v>
@@ -31884,7 +31884,7 @@
         <v>2</v>
       </c>
       <c r="AG298">
-        <v>0.4621487507210375</v>
+        <v>0.462</v>
       </c>
       <c r="AH298">
         <v>1</v>
@@ -31997,7 +31997,7 @@
         <v>3</v>
       </c>
       <c r="AG299">
-        <v>0.534711295367121</v>
+        <v>0.535</v>
       </c>
       <c r="AH299">
         <v>3</v>
@@ -32211,7 +32211,7 @@
         <v>3</v>
       </c>
       <c r="AG301">
-        <v>0.5952009951416775</v>
+        <v>0.595</v>
       </c>
       <c r="AH301">
         <v>4</v>
@@ -32324,7 +32324,7 @@
         <v>3</v>
       </c>
       <c r="AG302">
-        <v>0.4032863449597461</v>
+        <v>0.403</v>
       </c>
       <c r="AH302">
         <v>1</v>
@@ -32437,7 +32437,7 @@
         <v>2</v>
       </c>
       <c r="AG303">
-        <v>0.4551833660392847</v>
+        <v>0.455</v>
       </c>
       <c r="AH303">
         <v>1</v>
@@ -32550,7 +32550,7 @@
         <v>2</v>
       </c>
       <c r="AG304">
-        <v>0.513451376918869</v>
+        <v>0.513</v>
       </c>
       <c r="AH304">
         <v>3</v>
@@ -32663,7 +32663,7 @@
         <v>2</v>
       </c>
       <c r="AG305">
-        <v>0.5215524199835824</v>
+        <v>0.522</v>
       </c>
       <c r="AH305">
         <v>3</v>
@@ -32776,7 +32776,7 @@
         <v>2</v>
       </c>
       <c r="AG306">
-        <v>0.4759923165204525</v>
+        <v>0.476</v>
       </c>
       <c r="AH306">
         <v>2</v>
@@ -32889,7 +32889,7 @@
         <v>3</v>
       </c>
       <c r="AG307">
-        <v>0.5085846485993897</v>
+        <v>0.509</v>
       </c>
       <c r="AH307">
         <v>2</v>
@@ -33055,7 +33055,7 @@
         <v>3</v>
       </c>
       <c r="AG309">
-        <v>0.5296443093273185</v>
+        <v>0.53</v>
       </c>
       <c r="AH309">
         <v>3</v>
@@ -33221,7 +33221,7 @@
         <v>2</v>
       </c>
       <c r="AG311">
-        <v>0.5085846485993897</v>
+        <v>0.509</v>
       </c>
       <c r="AH311">
         <v>2</v>
@@ -33334,7 +33334,7 @@
         <v>2</v>
       </c>
       <c r="AG312">
-        <v>0.4889456792697737</v>
+        <v>0.489</v>
       </c>
       <c r="AH312">
         <v>2</v>
@@ -33447,7 +33447,7 @@
         <v>3</v>
       </c>
       <c r="AG313">
-        <v>0.5490116758896102</v>
+        <v>0.549</v>
       </c>
       <c r="AH313">
         <v>3</v>
@@ -33640,7 +33640,7 @@
         <v>2</v>
       </c>
       <c r="AG315">
-        <v>0.5175123793377103</v>
+        <v>0.518</v>
       </c>
       <c r="AH315">
         <v>3</v>
@@ -33753,7 +33753,7 @@
         <v>2</v>
       </c>
       <c r="AG316">
-        <v>0.3882437301540826</v>
+        <v>0.388</v>
       </c>
       <c r="AH316">
         <v>1</v>
@@ -33866,7 +33866,7 @@
         <v>3</v>
       </c>
       <c r="AG317">
-        <v>0.6108744292779009</v>
+        <v>0.611</v>
       </c>
       <c r="AH317">
         <v>4</v>
@@ -33979,7 +33979,7 @@
         <v>2</v>
       </c>
       <c r="AG318">
-        <v>0.3017486950215181</v>
+        <v>0.302</v>
       </c>
       <c r="AH318">
         <v>1</v>
@@ -34092,7 +34092,7 @@
         <v>2</v>
       </c>
       <c r="AG319">
-        <v>0.2876462436412086</v>
+        <v>0.288</v>
       </c>
       <c r="AH319">
         <v>1</v>
@@ -34205,7 +34205,7 @@
         <v>2</v>
       </c>
       <c r="AG320">
-        <v>0.4133147548301883</v>
+        <v>0.413</v>
       </c>
       <c r="AH320">
         <v>1</v>
@@ -34318,7 +34318,7 @@
         <v>2</v>
       </c>
       <c r="AG321">
-        <v>0.3355945783342608</v>
+        <v>0.336</v>
       </c>
       <c r="AH321">
         <v>1</v>
@@ -34431,7 +34431,7 @@
         <v>3</v>
       </c>
       <c r="AG322">
-        <v>0.522373712171248</v>
+        <v>0.522</v>
       </c>
       <c r="AH322">
         <v>3</v>
@@ -34544,7 +34544,7 @@
         <v>2</v>
       </c>
       <c r="AG323">
-        <v>0.4975239024187549</v>
+        <v>0.498</v>
       </c>
       <c r="AH323">
         <v>2</v>
@@ -34657,7 +34657,7 @@
         <v>1</v>
       </c>
       <c r="AG324">
-        <v>0.1325192784578049</v>
+        <v>0.133</v>
       </c>
       <c r="AH324">
         <v>1</v>
@@ -34770,7 +34770,7 @@
         <v>2</v>
       </c>
       <c r="AG325">
-        <v>0.5386698782107165</v>
+        <v>0.539</v>
       </c>
       <c r="AH325">
         <v>3</v>
@@ -34883,7 +34883,7 @@
         <v>2</v>
       </c>
       <c r="AG326">
-        <v>0.4862240049693496</v>
+        <v>0.486</v>
       </c>
       <c r="AH326">
         <v>2</v>
@@ -34996,7 +34996,7 @@
         <v>2</v>
       </c>
       <c r="AG327">
-        <v>0.2929738363848812</v>
+        <v>0.293</v>
       </c>
       <c r="AH327">
         <v>1</v>
@@ -35109,7 +35109,7 @@
         <v>3</v>
       </c>
       <c r="AG328">
-        <v>0.5409589717681001</v>
+        <v>0.541</v>
       </c>
       <c r="AH328">
         <v>3</v>
@@ -35222,7 +35222,7 @@
         <v>2</v>
       </c>
       <c r="AG329">
-        <v>0.4906305599603721</v>
+        <v>0.491</v>
       </c>
       <c r="AH329">
         <v>2</v>
@@ -35489,7 +35489,7 @@
         <v>2</v>
       </c>
       <c r="AG332">
-        <v>0.2829454265144389</v>
+        <v>0.283</v>
       </c>
       <c r="AH332">
         <v>1</v>
@@ -35602,7 +35602,7 @@
         <v>2</v>
       </c>
       <c r="AG333">
-        <v>0.5197161835555807</v>
+        <v>0.52</v>
       </c>
       <c r="AH333">
         <v>3</v>
@@ -35715,7 +35715,7 @@
         <v>2</v>
       </c>
       <c r="AG334">
-        <v>0.5119080169866875</v>
+        <v>0.512</v>
       </c>
       <c r="AH334">
         <v>2</v>
@@ -35828,7 +35828,7 @@
         <v>2</v>
       </c>
       <c r="AG335">
-        <v>0.3732011153484193</v>
+        <v>0.373</v>
       </c>
       <c r="AH335">
         <v>1</v>
@@ -35941,7 +35941,7 @@
         <v>3</v>
       </c>
       <c r="AG336">
-        <v>0.6140709849241044</v>
+        <v>0.614</v>
       </c>
       <c r="AH336">
         <v>4</v>
@@ -36054,7 +36054,7 @@
         <v>3</v>
       </c>
       <c r="AG337">
-        <v>0.5407382377464953</v>
+        <v>0.541</v>
       </c>
       <c r="AH337">
         <v>3</v>
@@ -36167,7 +36167,7 @@
         <v>2</v>
       </c>
       <c r="AG338">
-        <v>0.4296109208696569</v>
+        <v>0.43</v>
       </c>
       <c r="AH338">
         <v>1</v>
@@ -36333,7 +36333,7 @@
         <v>2</v>
       </c>
       <c r="AG340">
-        <v>0.3726638791053598</v>
+        <v>0.373</v>
       </c>
       <c r="AH340">
         <v>1</v>
@@ -36526,7 +36526,7 @@
         <v>2</v>
       </c>
       <c r="AG342">
-        <v>0.3976453644076222</v>
+        <v>0.398</v>
       </c>
       <c r="AH342">
         <v>1</v>
@@ -36639,7 +36639,7 @@
         <v>3</v>
       </c>
       <c r="AG343">
-        <v>0.4461577971558867</v>
+        <v>0.446</v>
       </c>
       <c r="AH343">
         <v>1</v>
@@ -36752,7 +36752,7 @@
         <v>2</v>
       </c>
       <c r="AG344">
-        <v>0.4168246982848431</v>
+        <v>0.417</v>
       </c>
       <c r="AH344">
         <v>1</v>
@@ -36865,7 +36865,7 @@
         <v>3</v>
       </c>
       <c r="AG345">
-        <v>0.7159578384203209</v>
+        <v>0.716</v>
       </c>
       <c r="AH345">
         <v>4</v>
@@ -36978,7 +36978,7 @@
         <v>3</v>
       </c>
       <c r="AG346">
-        <v>0.5916390856647015</v>
+        <v>0.592</v>
       </c>
       <c r="AH346">
         <v>4</v>
